--- a/jogos_2025-05-29.xlsx
+++ b/jogos_2025-05-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -184,6 +184,9 @@
     <t>DateTime</t>
   </si>
   <si>
+    <t>07:00</t>
+  </si>
+  <si>
     <t>07:30</t>
   </si>
   <si>
@@ -205,6 +208,9 @@
     <t>14:00</t>
   </si>
   <si>
+    <t>15:30</t>
+  </si>
+  <si>
     <t>16:00</t>
   </si>
   <si>
@@ -220,6 +226,9 @@
     <t>21:35</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
@@ -229,43 +238,46 @@
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Turkey 1. Lig</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Turkey 1. Lig</t>
+    <t>Italy Serie B</t>
   </si>
   <si>
     <t>South America Copa Libertadores</t>
   </si>
   <si>
-    <t>Paraguay Division Profesional</t>
-  </si>
-  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>2024/2025</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2024/2025</t>
+    <t>SuperSport United</t>
   </si>
   <si>
     <t>Torpedo Kutaisi</t>
@@ -280,52 +292,55 @@
     <t>Telavi</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Wisła Płock</t>
+  </si>
+  <si>
+    <t>Brann</t>
+  </si>
+  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Brann</t>
-  </si>
-  <si>
-    <t>Wisła Płock</t>
-  </si>
-  <si>
     <t>Afturelding</t>
   </si>
   <si>
     <t>ÍBV</t>
   </si>
   <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
     <t>Masr</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
     <t>El Geish</t>
   </si>
   <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
+    <t>Cremonese</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
@@ -334,30 +349,15 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Olimpia</t>
+  </si>
+  <si>
     <t>Peñarol</t>
   </si>
   <si>
-    <t>Atlético Tembetary</t>
-  </si>
-  <si>
     <t>Oued Akbou</t>
   </si>
   <si>
-    <t>Olimpia</t>
-  </si>
-  <si>
-    <t>Sportivo Luqueño</t>
-  </si>
-  <si>
-    <t>Sportivo Trinidense</t>
-  </si>
-  <si>
-    <t>General Caballero JLM</t>
-  </si>
-  <si>
-    <t>2 de Mayo</t>
-  </si>
-  <si>
     <t>Colo-Colo</t>
   </si>
   <si>
@@ -367,6 +367,9 @@
     <t>Ferroviária</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
     <t>Gareji</t>
   </si>
   <si>
@@ -379,52 +382,55 @@
     <t>Samgurali</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
     <t>FH</t>
   </si>
   <si>
+    <t>ÍA</t>
+  </si>
+  <si>
     <t>KA</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Coca-Cola</t>
   </si>
   <si>
+    <t>Bandırmaspor</t>
+  </si>
+  <si>
     <t>Mjøndalen</t>
   </si>
   <si>
-    <t>Bandırmaspor</t>
-  </si>
-  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
     <t>Kolkheti Poti</t>
   </si>
   <si>
-    <t>ENPPI</t>
+    <t>Spezia</t>
   </si>
   <si>
     <t>Miedź Legnica</t>
@@ -433,33 +439,15 @@
     <t>KR</t>
   </si>
   <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>Cerro Porteño</t>
-  </si>
-  <si>
     <t>CS Constantine</t>
   </si>
   <si>
-    <t>Deportivo Recoleta</t>
-  </si>
-  <si>
-    <t>Sportivo Ameliano</t>
-  </si>
-  <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>Guaraní</t>
-  </si>
-  <si>
-    <t>Nacional Asunción</t>
-  </si>
-  <si>
-    <t>Libertad</t>
-  </si>
-  <si>
     <t>Atlético Bucaramanga</t>
   </si>
   <si>
@@ -469,10 +457,10 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>suspended</t>
+  </si>
+  <si>
     <t>incomplete</t>
-  </si>
-  <si>
-    <t>suspended</t>
   </si>
   <si>
     <t>[]</t>
@@ -839,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD35"/>
+  <dimension ref="A1:BD31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -1020,13 +1008,13 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
         <v>117</v>
@@ -1044,127 +1032,127 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L2">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="M2">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB2">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="AC2">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO2">
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1173,13 +1161,13 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD2" s="3">
-        <v>45806.3125</v>
+        <v>45806.29166666666</v>
       </c>
     </row>
     <row r="3" spans="1:56">
@@ -1190,13 +1178,13 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
         <v>118</v>
@@ -1214,94 +1202,94 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="N3">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AD3">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL3">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1343,13 +1331,13 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="3">
-        <v>45806.45833333334</v>
+        <v>45806.3125</v>
       </c>
     </row>
     <row r="4" spans="1:56">
@@ -1357,16 +1345,16 @@
         <v>45806</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
         <v>119</v>
@@ -1384,94 +1372,94 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1483,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -1498,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX4">
         <v>0</v>
@@ -1513,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BD4" s="3">
         <v>45806.45833333334</v>
@@ -1530,13 +1518,13 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
         <v>120</v>
@@ -1554,94 +1542,94 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1683,13 +1671,13 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD5" s="3">
-        <v>45806.5</v>
+        <v>45806.45833333334</v>
       </c>
     </row>
     <row r="6" spans="1:56">
@@ -1703,10 +1691,10 @@
         <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
         <v>121</v>
@@ -1724,127 +1712,127 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L6">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL6">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR6">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT6">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU6">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV6">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY6">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1853,13 +1841,13 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BC6">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD6" s="3">
-        <v>45806.54166666666</v>
+        <v>45806.5</v>
       </c>
     </row>
     <row r="7" spans="1:56">
@@ -1867,16 +1855,16 @@
         <v>45806</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
         <v>122</v>
@@ -1894,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1969,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2037,16 +2025,16 @@
         <v>45806</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F8" t="s">
         <v>123</v>
@@ -2064,127 +2052,127 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L8">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="M8">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>4.26</v>
       </c>
       <c r="O8">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="P8">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R8">
         <v>1.3</v>
       </c>
       <c r="S8">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U8">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V8">
+        <v>5.5</v>
+      </c>
+      <c r="W8">
+        <v>1.1</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>11</v>
+      </c>
+      <c r="Z8">
+        <v>1.25</v>
+      </c>
+      <c r="AA8">
+        <v>3.6</v>
+      </c>
+      <c r="AB8">
+        <v>1.8</v>
+      </c>
+      <c r="AC8">
+        <v>1.96</v>
+      </c>
+      <c r="AD8">
+        <v>3.1</v>
+      </c>
+      <c r="AE8">
+        <v>1.33</v>
+      </c>
+      <c r="AF8">
+        <v>1.75</v>
+      </c>
+      <c r="AG8">
+        <v>2</v>
+      </c>
+      <c r="AH8">
         <v>6</v>
       </c>
-      <c r="W8">
+      <c r="AI8">
         <v>1.13</v>
       </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>10</v>
-      </c>
-      <c r="Z8">
-        <v>1.2</v>
-      </c>
-      <c r="AA8">
-        <v>4.33</v>
-      </c>
-      <c r="AB8">
-        <v>1.6</v>
-      </c>
-      <c r="AC8">
-        <v>2.1</v>
-      </c>
-      <c r="AD8">
-        <v>2.55</v>
-      </c>
-      <c r="AE8">
-        <v>1.5</v>
-      </c>
-      <c r="AF8">
-        <v>1.62</v>
-      </c>
-      <c r="AG8">
-        <v>2.2</v>
-      </c>
-      <c r="AH8">
-        <v>4.5</v>
-      </c>
-      <c r="AI8">
-        <v>1.2</v>
-      </c>
       <c r="AJ8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN8">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2193,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BC8">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BD8" s="3">
         <v>45806.54166666666</v>
@@ -2207,16 +2195,16 @@
         <v>45806</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
         <v>124</v>
@@ -2234,127 +2222,127 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L9">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="M9">
-        <v>3.69</v>
+        <v>3.58</v>
       </c>
       <c r="N9">
-        <v>4.26</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2363,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD9" s="3">
         <v>45806.54166666666</v>
@@ -2380,13 +2368,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
         <v>125</v>
@@ -2404,127 +2392,127 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M10">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="N10">
-        <v>1.61</v>
+        <v>2.49</v>
       </c>
       <c r="O10">
+        <v>2.1</v>
+      </c>
+      <c r="P10">
+        <v>8.5</v>
+      </c>
+      <c r="Q10">
+        <v>1.73</v>
+      </c>
+      <c r="R10">
+        <v>1.33</v>
+      </c>
+      <c r="S10">
+        <v>3.25</v>
+      </c>
+      <c r="T10">
         <v>2.63</v>
       </c>
-      <c r="P10">
-        <v>17.5</v>
-      </c>
-      <c r="Q10">
+      <c r="U10">
         <v>1.44</v>
       </c>
-      <c r="R10">
-        <v>1.2</v>
-      </c>
-      <c r="S10">
-        <v>4.1</v>
-      </c>
-      <c r="T10">
-        <v>1.99</v>
-      </c>
-      <c r="U10">
-        <v>1.81</v>
-      </c>
       <c r="V10">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AA10">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB10">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="AC10">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD10">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AE10">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="AF10">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH10">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="AI10">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AJ10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL10">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AM10">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AN10">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2533,13 +2521,13 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="BC10">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="BD10" s="3">
-        <v>45806.55208333334</v>
+        <v>45806.54166666666</v>
       </c>
     </row>
     <row r="11" spans="1:56">
@@ -2547,16 +2535,16 @@
         <v>45806</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
         <v>126</v>
@@ -2574,94 +2562,94 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>4.2</v>
+      </c>
+      <c r="N11">
+        <v>1.61</v>
+      </c>
+      <c r="O11">
+        <v>2.63</v>
+      </c>
+      <c r="P11">
+        <v>17.5</v>
+      </c>
+      <c r="Q11">
+        <v>1.44</v>
+      </c>
+      <c r="R11">
+        <v>1.2</v>
+      </c>
+      <c r="S11">
+        <v>4.1</v>
+      </c>
+      <c r="T11">
+        <v>1.98</v>
+      </c>
+      <c r="U11">
+        <v>1.82</v>
+      </c>
+      <c r="V11">
+        <v>3.8</v>
+      </c>
+      <c r="W11">
+        <v>1.22</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>23</v>
+      </c>
+      <c r="Z11">
+        <v>1.04</v>
+      </c>
+      <c r="AA11">
+        <v>6</v>
+      </c>
+      <c r="AB11">
+        <v>1.32</v>
+      </c>
+      <c r="AC11">
+        <v>2.9</v>
+      </c>
+      <c r="AD11">
+        <v>1.83</v>
+      </c>
+      <c r="AE11">
+        <v>1.8</v>
+      </c>
+      <c r="AF11">
+        <v>1.4</v>
+      </c>
+      <c r="AG11">
         <v>2.8</v>
       </c>
-      <c r="M11">
-        <v>3.55</v>
-      </c>
-      <c r="N11">
-        <v>2.12</v>
-      </c>
-      <c r="O11">
-        <v>1.95</v>
-      </c>
-      <c r="P11">
-        <v>17</v>
-      </c>
-      <c r="Q11">
-        <v>1.88</v>
-      </c>
-      <c r="R11">
-        <v>1.25</v>
-      </c>
-      <c r="S11">
-        <v>3.6</v>
-      </c>
-      <c r="T11">
-        <v>1.97</v>
-      </c>
-      <c r="U11">
-        <v>1.75</v>
-      </c>
-      <c r="V11">
-        <v>4.1</v>
-      </c>
-      <c r="W11">
-        <v>1.2</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>15</v>
-      </c>
-      <c r="Z11">
-        <v>1.08</v>
-      </c>
-      <c r="AA11">
-        <v>5.75</v>
-      </c>
-      <c r="AB11">
-        <v>1.38</v>
-      </c>
-      <c r="AC11">
-        <v>2.8</v>
-      </c>
-      <c r="AD11">
-        <v>2.05</v>
-      </c>
-      <c r="AE11">
-        <v>1.65</v>
-      </c>
-      <c r="AF11">
+      <c r="AH11">
+        <v>2.94</v>
+      </c>
+      <c r="AI11">
         <v>1.33</v>
       </c>
-      <c r="AG11">
-        <v>3</v>
-      </c>
-      <c r="AH11">
-        <v>3.1</v>
-      </c>
-      <c r="AI11">
-        <v>1.32</v>
-      </c>
       <c r="AJ11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL11">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="AM11">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN11">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AO11">
         <v>-1</v>
@@ -2703,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="BC11">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="BD11" s="3">
         <v>45806.55208333334</v>
@@ -2717,16 +2705,16 @@
         <v>45806</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
         <v>127</v>
@@ -2744,94 +2732,94 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L12">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="M12">
+        <v>3.55</v>
+      </c>
+      <c r="N12">
+        <v>2.12</v>
+      </c>
+      <c r="O12">
+        <v>1.95</v>
+      </c>
+      <c r="P12">
+        <v>17</v>
+      </c>
+      <c r="Q12">
+        <v>1.88</v>
+      </c>
+      <c r="R12">
+        <v>1.25</v>
+      </c>
+      <c r="S12">
         <v>3.6</v>
       </c>
-      <c r="N12">
-        <v>2.5</v>
-      </c>
-      <c r="O12">
-        <v>1.67</v>
-      </c>
-      <c r="P12">
-        <v>14.5</v>
-      </c>
-      <c r="Q12">
-        <v>2.2</v>
-      </c>
-      <c r="R12">
-        <v>1.27</v>
-      </c>
-      <c r="S12">
-        <v>3.4</v>
-      </c>
       <c r="T12">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="U12">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="V12">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z12">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AB12">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AC12">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AD12">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AE12">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF12">
+        <v>1.4</v>
+      </c>
+      <c r="AG12">
+        <v>2.8</v>
+      </c>
+      <c r="AH12">
+        <v>3.5</v>
+      </c>
+      <c r="AI12">
+        <v>1.3</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL12">
+        <v>1.25</v>
+      </c>
+      <c r="AM12">
+        <v>1.26</v>
+      </c>
+      <c r="AN12">
         <v>1.44</v>
-      </c>
-      <c r="AG12">
-        <v>2.63</v>
-      </c>
-      <c r="AH12">
-        <v>3.9</v>
-      </c>
-      <c r="AI12">
-        <v>1.22</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL12">
-        <v>1.29</v>
-      </c>
-      <c r="AM12">
-        <v>1.25</v>
-      </c>
-      <c r="AN12">
-        <v>1.67</v>
       </c>
       <c r="AO12">
         <v>-1</v>
@@ -2849,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AU12">
         <v>0</v>
@@ -2864,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2873,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="BC12">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="BD12" s="3">
         <v>45806.55208333334</v>
@@ -2887,16 +2875,16 @@
         <v>45806</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
         <v>128</v>
@@ -2914,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L13">
         <v>1.3</v>
@@ -2935,16 +2923,16 @@
         <v>3.2</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S13">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="T13">
         <v>1.85</v>
       </c>
       <c r="U13">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V13">
         <v>3.6</v>
@@ -2956,19 +2944,19 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z13">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AA13">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>1.3</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD13">
         <v>1.75</v>
@@ -2980,28 +2968,28 @@
         <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH13">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AI13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AJ13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL13">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AM13">
         <v>1.14</v>
       </c>
       <c r="AN13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AO13">
         <v>-1</v>
@@ -3060,13 +3048,13 @@
         <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" t="s">
         <v>129</v>
@@ -3084,94 +3072,94 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L14">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="M14">
         <v>3.6</v>
       </c>
       <c r="N14">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="P14">
+        <v>14.5</v>
+      </c>
+      <c r="Q14">
+        <v>2.2</v>
+      </c>
+      <c r="R14">
+        <v>1.25</v>
+      </c>
+      <c r="S14">
+        <v>3.3</v>
+      </c>
+      <c r="T14">
+        <v>2.25</v>
+      </c>
+      <c r="U14">
+        <v>1.62</v>
+      </c>
+      <c r="V14">
+        <v>4.6</v>
+      </c>
+      <c r="W14">
+        <v>1.15</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
         <v>12</v>
       </c>
-      <c r="Q14">
-        <v>2.1</v>
-      </c>
-      <c r="R14">
-        <v>1.29</v>
-      </c>
-      <c r="S14">
-        <v>3.4</v>
-      </c>
-      <c r="T14">
-        <v>2.49</v>
-      </c>
-      <c r="U14">
+      <c r="Z14">
+        <v>1.09</v>
+      </c>
+      <c r="AA14">
+        <v>5</v>
+      </c>
+      <c r="AB14">
         <v>1.5</v>
       </c>
-      <c r="V14">
-        <v>5.7</v>
-      </c>
-      <c r="W14">
-        <v>1.12</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>12.5</v>
-      </c>
-      <c r="Z14">
-        <v>1.2</v>
-      </c>
-      <c r="AA14">
-        <v>4.16</v>
-      </c>
-      <c r="AB14">
-        <v>1.68</v>
-      </c>
       <c r="AC14">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="AD14">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="AE14">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AG14">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AH14">
-        <v>4.63</v>
+        <v>3.5</v>
       </c>
       <c r="AI14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL14">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AM14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN14">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AO14">
         <v>-1</v>
@@ -3189,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AU14">
         <v>0</v>
@@ -3204,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3213,13 +3201,13 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="BC14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD14" s="3">
-        <v>45806.5625</v>
+        <v>45806.55208333334</v>
       </c>
     </row>
     <row r="15" spans="1:56">
@@ -3230,13 +3218,13 @@
         <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
         <v>130</v>
@@ -3254,127 +3242,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L15">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="M15">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="N15">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="O15">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="P15">
-        <v>5.25</v>
+        <v>12</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="R15">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="S15">
+        <v>3.4</v>
+      </c>
+      <c r="T15">
+        <v>2.49</v>
+      </c>
+      <c r="U15">
+        <v>1.5</v>
+      </c>
+      <c r="V15">
+        <v>5.7</v>
+      </c>
+      <c r="W15">
+        <v>1.12</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>12.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.2</v>
+      </c>
+      <c r="AA15">
+        <v>4.16</v>
+      </c>
+      <c r="AB15">
+        <v>1.67</v>
+      </c>
+      <c r="AC15">
         <v>2.1</v>
       </c>
-      <c r="T15">
-        <v>3.8</v>
-      </c>
-      <c r="U15">
+      <c r="AD15">
+        <v>2.64</v>
+      </c>
+      <c r="AE15">
+        <v>1.44</v>
+      </c>
+      <c r="AF15">
+        <v>1.57</v>
+      </c>
+      <c r="AG15">
+        <v>2.34</v>
+      </c>
+      <c r="AH15">
+        <v>4.63</v>
+      </c>
+      <c r="AI15">
+        <v>1.17</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL15">
+        <v>1.36</v>
+      </c>
+      <c r="AM15">
         <v>1.22</v>
       </c>
-      <c r="V15">
-        <v>11</v>
-      </c>
-      <c r="W15">
-        <v>1.02</v>
-      </c>
-      <c r="X15">
-        <v>1.11</v>
-      </c>
-      <c r="Y15">
-        <v>5.5</v>
-      </c>
-      <c r="Z15">
-        <v>1.63</v>
-      </c>
-      <c r="AA15">
-        <v>2.19</v>
-      </c>
-      <c r="AB15">
-        <v>2.74</v>
-      </c>
-      <c r="AC15">
-        <v>1.35</v>
-      </c>
-      <c r="AD15">
-        <v>5.6</v>
-      </c>
-      <c r="AE15">
-        <v>1.11</v>
-      </c>
-      <c r="AF15">
-        <v>2.3</v>
-      </c>
-      <c r="AG15">
-        <v>1.55</v>
-      </c>
-      <c r="AH15">
-        <v>12.5</v>
-      </c>
-      <c r="AI15">
-        <v>1.01</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL15">
-        <v>1.42</v>
-      </c>
-      <c r="AM15">
-        <v>1.38</v>
-      </c>
       <c r="AN15">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3383,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BC15">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" s="3">
-        <v>45806.58333333334</v>
+        <v>45806.5625</v>
       </c>
     </row>
     <row r="16" spans="1:56">
@@ -3397,16 +3385,16 @@
         <v>45806</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
         <v>131</v>
@@ -3424,37 +3412,37 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L16">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="N16">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P16">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q16">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="R16">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="S16">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V16">
         <v>11</v>
@@ -3463,55 +3451,55 @@
         <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Y16">
-        <v>4.33</v>
+        <v>5.35</v>
       </c>
       <c r="Z16">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA16">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AC16">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG16">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AI16">
         <v>1.01</v>
       </c>
       <c r="AJ16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL16">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AM16">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AN16">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AO16">
         <v>-1</v>
@@ -3553,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="BC16">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="BD16" s="3">
         <v>45806.58333333334</v>
@@ -3567,16 +3555,16 @@
         <v>45806</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
         <v>132</v>
@@ -3594,127 +3582,127 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L17">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="M17">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="N17">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="O17">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA17">
-        <v>4.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL17">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3723,10 +3711,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BD17" s="3">
         <v>45806.58333333334</v>
@@ -3737,16 +3725,16 @@
         <v>45806</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
         <v>133</v>
@@ -3764,94 +3752,94 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L18">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
       <c r="M18">
-        <v>3.48</v>
+        <v>2.41</v>
       </c>
       <c r="N18">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="O18">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="P18">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R18">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="S18">
-        <v>3.24</v>
+        <v>1.91</v>
       </c>
       <c r="T18">
-        <v>2.61</v>
+        <v>4.2</v>
       </c>
       <c r="U18">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="V18">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="Y18">
-        <v>10.4</v>
+        <v>3.8</v>
       </c>
       <c r="Z18">
-        <v>1.23</v>
+        <v>1.77</v>
       </c>
       <c r="AA18">
-        <v>3.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="AC18">
-        <v>2.03</v>
+        <v>1.29</v>
       </c>
       <c r="AD18">
-        <v>2.85</v>
+        <v>6.5</v>
       </c>
       <c r="AE18">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="AG18">
-        <v>2.27</v>
+        <v>1.5</v>
       </c>
       <c r="AH18">
-        <v>5.17</v>
+        <v>15</v>
       </c>
       <c r="AI18">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AJ18" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK18" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL18">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AM18">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AN18">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AO18">
         <v>-1</v>
@@ -3893,10 +3881,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="BC18">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="BD18" s="3">
         <v>45806.58333333334</v>
@@ -3907,16 +3895,16 @@
         <v>45806</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
         <v>134</v>
@@ -3934,91 +3922,91 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L19">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="M19">
-        <v>2.62</v>
+        <v>3.48</v>
       </c>
       <c r="N19">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="O19">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="Q19">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
+        <v>1.32</v>
+      </c>
+      <c r="S19">
+        <v>3.24</v>
+      </c>
+      <c r="T19">
+        <v>2.61</v>
+      </c>
+      <c r="U19">
+        <v>1.46</v>
+      </c>
+      <c r="V19">
+        <v>6.3</v>
+      </c>
+      <c r="W19">
+        <v>1.06</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>10.4</v>
+      </c>
+      <c r="Z19">
+        <v>1.23</v>
+      </c>
+      <c r="AA19">
+        <v>3.92</v>
+      </c>
+      <c r="AB19">
         <v>1.76</v>
       </c>
-      <c r="S19">
-        <v>2</v>
-      </c>
-      <c r="T19">
-        <v>4.7</v>
-      </c>
-      <c r="U19">
-        <v>1.15</v>
-      </c>
-      <c r="V19">
-        <v>12</v>
-      </c>
-      <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>1.17</v>
-      </c>
-      <c r="Y19">
-        <v>4.65</v>
-      </c>
-      <c r="Z19">
-        <v>1.77</v>
-      </c>
-      <c r="AA19">
-        <v>1.93</v>
-      </c>
-      <c r="AB19">
-        <v>3.33</v>
-      </c>
       <c r="AC19">
-        <v>1.29</v>
+        <v>2.03</v>
       </c>
       <c r="AD19">
-        <v>7</v>
+        <v>2.85</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="AF19">
-        <v>2.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
+        <v>2.27</v>
+      </c>
+      <c r="AH19">
+        <v>5.17</v>
+      </c>
+      <c r="AI19">
+        <v>1.14</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL19">
         <v>1.4</v>
       </c>
-      <c r="AH19">
-        <v>17.5</v>
-      </c>
-      <c r="AI19">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL19">
-        <v>1.44</v>
-      </c>
       <c r="AM19">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AN19">
         <v>1.6</v>
@@ -4063,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="BC19">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="BD19" s="3">
         <v>45806.58333333334</v>
@@ -4077,16 +4065,16 @@
         <v>45806</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
         <v>135</v>
@@ -4104,127 +4092,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ20" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK20" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4233,10 +4221,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BD20" s="3">
         <v>45806.58333333334</v>
@@ -4247,16 +4235,16 @@
         <v>45806</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
         <v>136</v>
@@ -4274,94 +4262,94 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L21">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="M21">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="N21">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Z21">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AA21">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO21">
         <v>-1</v>
@@ -4403,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BD21" s="3">
         <v>45806.58333333334</v>
@@ -4420,13 +4408,13 @@
         <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F22" t="s">
         <v>137</v>
@@ -4444,16 +4432,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L22">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="M22">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N22">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4495,10 +4483,10 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -4519,10 +4507,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4579,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="BD22" s="3">
-        <v>45806.66666666666</v>
+        <v>45806.58333333334</v>
       </c>
     </row>
     <row r="23" spans="1:56">
@@ -4590,13 +4578,13 @@
         <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
         <v>138</v>
@@ -4614,127 +4602,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L23">
-        <v>2.55</v>
+        <v>3.02</v>
       </c>
       <c r="M23">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="N23">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="O23">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="P23">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="T23">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="U23">
+        <v>1.41</v>
+      </c>
+      <c r="V23">
+        <v>6.75</v>
+      </c>
+      <c r="W23">
+        <v>1.09</v>
+      </c>
+      <c r="X23">
+        <v>1.06</v>
+      </c>
+      <c r="Y23">
+        <v>8.5</v>
+      </c>
+      <c r="Z23">
+        <v>1.28</v>
+      </c>
+      <c r="AA23">
+        <v>3.5</v>
+      </c>
+      <c r="AB23">
+        <v>1.82</v>
+      </c>
+      <c r="AC23">
+        <v>1.92</v>
+      </c>
+      <c r="AD23">
+        <v>3.1</v>
+      </c>
+      <c r="AE23">
+        <v>1.35</v>
+      </c>
+      <c r="AF23">
+        <v>1.68</v>
+      </c>
+      <c r="AG23">
         <v>2.05</v>
       </c>
-      <c r="V23">
-        <v>3.3</v>
-      </c>
-      <c r="W23">
-        <v>1.28</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>29</v>
-      </c>
-      <c r="Z23">
-        <v>1.06</v>
-      </c>
-      <c r="AA23">
-        <v>7.5</v>
-      </c>
-      <c r="AB23">
-        <v>1.3</v>
-      </c>
-      <c r="AC23">
-        <v>3.4</v>
-      </c>
-      <c r="AD23">
-        <v>1.65</v>
-      </c>
-      <c r="AE23">
-        <v>2.05</v>
-      </c>
-      <c r="AF23">
-        <v>1.3</v>
-      </c>
-      <c r="AG23">
-        <v>3.4</v>
-      </c>
       <c r="AH23">
-        <v>2.45</v>
+        <v>5.75</v>
       </c>
       <c r="AI23">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AJ23" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK23" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL23">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AM23">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AN23">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4743,13 +4731,13 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="BC23">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="BD23" s="3">
-        <v>45806.67708333334</v>
+        <v>45806.64583333334</v>
       </c>
     </row>
     <row r="24" spans="1:56">
@@ -4760,13 +4748,13 @@
         <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
         <v>139</v>
@@ -4784,127 +4772,127 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L24">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="M24">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N24">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="O24">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="P24">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R24">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="S24">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="U24">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="V24">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="Z24">
+        <v>1.18</v>
+      </c>
+      <c r="AA24">
+        <v>4.5</v>
+      </c>
+      <c r="AB24">
+        <v>1.57</v>
+      </c>
+      <c r="AC24">
+        <v>2.3</v>
+      </c>
+      <c r="AD24">
+        <v>2.45</v>
+      </c>
+      <c r="AE24">
         <v>1.5</v>
       </c>
-      <c r="AA24">
-        <v>2.5</v>
-      </c>
-      <c r="AB24">
-        <v>2.3</v>
-      </c>
-      <c r="AC24">
-        <v>1.5</v>
-      </c>
-      <c r="AD24">
-        <v>5</v>
-      </c>
-      <c r="AE24">
-        <v>1.17</v>
-      </c>
       <c r="AF24">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AH24">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AI24">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM24">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AN24">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ24">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR24">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS24">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AT24">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU24">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV24">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW24">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX24">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY24">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -4913,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="BC24">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="BD24" s="3">
-        <v>45806.79166666666</v>
+        <v>45806.66666666666</v>
       </c>
     </row>
     <row r="25" spans="1:56">
@@ -4927,16 +4915,16 @@
         <v>45806</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s">
         <v>140</v>
@@ -4954,94 +4942,94 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AJ25" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK25" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO25">
         <v>-1</v>
@@ -5083,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD25" s="3">
-        <v>45806.79166666666</v>
+        <v>45806.67708333334</v>
       </c>
     </row>
     <row r="26" spans="1:56">
@@ -5097,16 +5085,16 @@
         <v>45806</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
         <v>141</v>
@@ -5124,127 +5112,127 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ26" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK26" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -5253,10 +5241,10 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BD26" s="3">
         <v>45806.79166666666</v>
@@ -5267,16 +5255,16 @@
         <v>45806</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
         <v>142</v>
@@ -5294,127 +5282,127 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ27" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK27" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5423,10 +5411,10 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD27" s="3">
         <v>45806.79166666666</v>
@@ -5437,16 +5425,16 @@
         <v>45806</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
         <v>143</v>
@@ -5464,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -5539,10 +5527,10 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK28" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5607,16 +5595,16 @@
         <v>45806</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
         <v>144</v>
@@ -5634,142 +5622,142 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L29">
-        <v>1.14</v>
+        <v>2.49</v>
       </c>
       <c r="M29">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="N29">
-        <v>9.800000000000001</v>
+        <v>2.41</v>
       </c>
       <c r="O29">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="P29">
-        <v>23</v>
+        <v>9.25</v>
       </c>
       <c r="Q29">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="R29">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="S29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="V29">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>29</v>
+        <v>10.2</v>
       </c>
       <c r="Z29">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AA29">
-        <v>7.5</v>
+        <v>3.48</v>
       </c>
       <c r="AB29">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="AC29">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD29">
+        <v>3.12</v>
+      </c>
+      <c r="AE29">
+        <v>1.29</v>
+      </c>
+      <c r="AF29">
         <v>1.7</v>
       </c>
-      <c r="AE29">
-        <v>1.95</v>
-      </c>
-      <c r="AF29">
-        <v>1.75</v>
-      </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH29">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="AI29">
-        <v>1.48</v>
+        <v>1.06</v>
       </c>
       <c r="AJ29" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK29" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL29">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="AM29">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AN29">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AQ29">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
+        <v>1.82</v>
+      </c>
+      <c r="AS29">
+        <v>2.3</v>
+      </c>
+      <c r="AT29">
+        <v>2.9</v>
+      </c>
+      <c r="AU29">
+        <v>3.15</v>
+      </c>
+      <c r="AV29">
+        <v>2.38</v>
+      </c>
+      <c r="AW29">
+        <v>1.86</v>
+      </c>
+      <c r="AX29">
+        <v>1.54</v>
+      </c>
+      <c r="AY29">
+        <v>1.34</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
         <v>2.1</v>
       </c>
-      <c r="AS29">
-        <v>2.65</v>
-      </c>
-      <c r="AT29">
-        <v>3.45</v>
-      </c>
-      <c r="AU29">
-        <v>2.65</v>
-      </c>
-      <c r="AV29">
-        <v>2</v>
-      </c>
-      <c r="AW29">
-        <v>1.63</v>
-      </c>
-      <c r="AX29">
-        <v>1.41</v>
-      </c>
-      <c r="AY29">
-        <v>1.25</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.2</v>
-      </c>
       <c r="BC29">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="BD29" s="3">
-        <v>45806.79166666666</v>
+        <v>45806.89583333334</v>
       </c>
     </row>
     <row r="30" spans="1:56">
@@ -5777,16 +5765,16 @@
         <v>45806</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
         <v>145</v>
@@ -5804,127 +5792,127 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ30" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK30" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ30">
         <v>0</v>
@@ -5933,13 +5921,13 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BD30" s="3">
-        <v>45806.79166666666</v>
+        <v>45806.89583333334</v>
       </c>
     </row>
     <row r="31" spans="1:56">
@@ -5947,16 +5935,16 @@
         <v>45806</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
         <v>146</v>
@@ -5974,127 +5962,127 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ31" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AK31" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6103,692 +6091,12 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD31" s="3">
-        <v>45806.79166666666</v>
-      </c>
-    </row>
-    <row r="32" spans="1:56">
-      <c r="A32" s="2">
-        <v>45806</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" t="s">
-        <v>82</v>
-      </c>
-      <c r="E32" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" t="s">
-        <v>147</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
-        <v>152</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>-1</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
-      <c r="BC32">
-        <v>0</v>
-      </c>
-      <c r="BD32" s="3">
-        <v>45806.79166666666</v>
-      </c>
-    </row>
-    <row r="33" spans="1:56">
-      <c r="A33" s="2">
-        <v>45806</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" t="s">
-        <v>148</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
-        <v>151</v>
-      </c>
-      <c r="L33">
-        <v>2.49</v>
-      </c>
-      <c r="M33">
-        <v>3.3</v>
-      </c>
-      <c r="N33">
-        <v>2.41</v>
-      </c>
-      <c r="O33">
-        <v>2.1</v>
-      </c>
-      <c r="P33">
-        <v>9.25</v>
-      </c>
-      <c r="Q33">
-        <v>1.83</v>
-      </c>
-      <c r="R33">
-        <v>1.36</v>
-      </c>
-      <c r="S33">
-        <v>3</v>
-      </c>
-      <c r="T33">
-        <v>2.75</v>
-      </c>
-      <c r="U33">
-        <v>1.4</v>
-      </c>
-      <c r="V33">
-        <v>7</v>
-      </c>
-      <c r="W33">
-        <v>1.1</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>10.2</v>
-      </c>
-      <c r="Z33">
-        <v>1.24</v>
-      </c>
-      <c r="AA33">
-        <v>3.48</v>
-      </c>
-      <c r="AB33">
-        <v>1.85</v>
-      </c>
-      <c r="AC33">
-        <v>1.85</v>
-      </c>
-      <c r="AD33">
-        <v>3.12</v>
-      </c>
-      <c r="AE33">
-        <v>1.29</v>
-      </c>
-      <c r="AF33">
-        <v>1.7</v>
-      </c>
-      <c r="AG33">
-        <v>2.05</v>
-      </c>
-      <c r="AH33">
-        <v>6.1</v>
-      </c>
-      <c r="AI33">
-        <v>1.06</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL33">
-        <v>1.5</v>
-      </c>
-      <c r="AM33">
-        <v>1.3</v>
-      </c>
-      <c r="AN33">
-        <v>1.44</v>
-      </c>
-      <c r="AO33">
-        <v>-1</v>
-      </c>
-      <c r="AP33">
-        <v>1.29</v>
-      </c>
-      <c r="AQ33">
-        <v>1.5</v>
-      </c>
-      <c r="AR33">
-        <v>1.82</v>
-      </c>
-      <c r="AS33">
-        <v>2.3</v>
-      </c>
-      <c r="AT33">
-        <v>2.9</v>
-      </c>
-      <c r="AU33">
-        <v>3.15</v>
-      </c>
-      <c r="AV33">
-        <v>2.38</v>
-      </c>
-      <c r="AW33">
-        <v>1.86</v>
-      </c>
-      <c r="AX33">
-        <v>1.54</v>
-      </c>
-      <c r="AY33">
-        <v>1.34</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>2.1</v>
-      </c>
-      <c r="BC33">
-        <v>1.83</v>
-      </c>
-      <c r="BD33" s="3">
-        <v>45806.89583333334</v>
-      </c>
-    </row>
-    <row r="34" spans="1:56">
-      <c r="A34" s="2">
-        <v>45806</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34" t="s">
-        <v>149</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
-        <v>151</v>
-      </c>
-      <c r="L34">
-        <v>1.78</v>
-      </c>
-      <c r="M34">
-        <v>3.26</v>
-      </c>
-      <c r="N34">
-        <v>4</v>
-      </c>
-      <c r="O34">
-        <v>1.65</v>
-      </c>
-      <c r="P34">
-        <v>8.25</v>
-      </c>
-      <c r="Q34">
-        <v>2.6</v>
-      </c>
-      <c r="R34">
-        <v>1.41</v>
-      </c>
-      <c r="S34">
-        <v>2.65</v>
-      </c>
-      <c r="T34">
-        <v>2.85</v>
-      </c>
-      <c r="U34">
-        <v>1.37</v>
-      </c>
-      <c r="V34">
-        <v>7.5</v>
-      </c>
-      <c r="W34">
-        <v>1.08</v>
-      </c>
-      <c r="X34">
-        <v>1.06</v>
-      </c>
-      <c r="Y34">
-        <v>8.25</v>
-      </c>
-      <c r="Z34">
-        <v>1.33</v>
-      </c>
-      <c r="AA34">
-        <v>3.1</v>
-      </c>
-      <c r="AB34">
-        <v>1.94</v>
-      </c>
-      <c r="AC34">
-        <v>1.76</v>
-      </c>
-      <c r="AD34">
-        <v>3.4</v>
-      </c>
-      <c r="AE34">
-        <v>1.27</v>
-      </c>
-      <c r="AF34">
-        <v>1.85</v>
-      </c>
-      <c r="AG34">
-        <v>1.82</v>
-      </c>
-      <c r="AH34">
-        <v>6.5</v>
-      </c>
-      <c r="AI34">
-        <v>1.09</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL34">
-        <v>1.22</v>
-      </c>
-      <c r="AM34">
-        <v>1.3</v>
-      </c>
-      <c r="AN34">
-        <v>1.85</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>1.28</v>
-      </c>
-      <c r="AQ34">
-        <v>1.5</v>
-      </c>
-      <c r="AR34">
-        <v>1.81</v>
-      </c>
-      <c r="AS34">
-        <v>2.28</v>
-      </c>
-      <c r="AT34">
-        <v>2.9</v>
-      </c>
-      <c r="AU34">
-        <v>3.2</v>
-      </c>
-      <c r="AV34">
-        <v>2.4</v>
-      </c>
-      <c r="AW34">
-        <v>1.88</v>
-      </c>
-      <c r="AX34">
-        <v>1.55</v>
-      </c>
-      <c r="AY34">
-        <v>1.35</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>1.65</v>
-      </c>
-      <c r="BC34">
-        <v>2.6</v>
-      </c>
-      <c r="BD34" s="3">
-        <v>45806.89583333334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:56">
-      <c r="A35" s="2">
-        <v>45806</v>
-      </c>
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" t="s">
-        <v>116</v>
-      </c>
-      <c r="F35" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35" t="s">
-        <v>151</v>
-      </c>
-      <c r="L35">
-        <v>1.81</v>
-      </c>
-      <c r="M35">
-        <v>3.13</v>
-      </c>
-      <c r="N35">
-        <v>4.1</v>
-      </c>
-      <c r="O35">
-        <v>1.65</v>
-      </c>
-      <c r="P35">
-        <v>6.75</v>
-      </c>
-      <c r="Q35">
-        <v>2.75</v>
-      </c>
-      <c r="R35">
-        <v>1.5</v>
-      </c>
-      <c r="S35">
-        <v>2.4</v>
-      </c>
-      <c r="T35">
-        <v>3.3</v>
-      </c>
-      <c r="U35">
-        <v>1.29</v>
-      </c>
-      <c r="V35">
-        <v>8.5</v>
-      </c>
-      <c r="W35">
-        <v>1.04</v>
-      </c>
-      <c r="X35">
-        <v>1.08</v>
-      </c>
-      <c r="Y35">
-        <v>6.5</v>
-      </c>
-      <c r="Z35">
-        <v>1.46</v>
-      </c>
-      <c r="AA35">
-        <v>2.5</v>
-      </c>
-      <c r="AB35">
-        <v>2.3</v>
-      </c>
-      <c r="AC35">
-        <v>1.5</v>
-      </c>
-      <c r="AD35">
-        <v>4.33</v>
-      </c>
-      <c r="AE35">
-        <v>1.17</v>
-      </c>
-      <c r="AF35">
-        <v>2.2</v>
-      </c>
-      <c r="AG35">
-        <v>1.62</v>
-      </c>
-      <c r="AH35">
-        <v>9</v>
-      </c>
-      <c r="AI35">
-        <v>1.03</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL35">
-        <v>1.3</v>
-      </c>
-      <c r="AM35">
-        <v>1.31</v>
-      </c>
-      <c r="AN35">
-        <v>1.95</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>1.32</v>
-      </c>
-      <c r="AQ35">
-        <v>1.56</v>
-      </c>
-      <c r="AR35">
-        <v>1.92</v>
-      </c>
-      <c r="AS35">
-        <v>2.4</v>
-      </c>
-      <c r="AT35">
-        <v>3.15</v>
-      </c>
-      <c r="AU35">
-        <v>3</v>
-      </c>
-      <c r="AV35">
-        <v>2.23</v>
-      </c>
-      <c r="AW35">
-        <v>1.77</v>
-      </c>
-      <c r="AX35">
-        <v>1.49</v>
-      </c>
-      <c r="AY35">
-        <v>1.3</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.65</v>
-      </c>
-      <c r="BC35">
-        <v>2.75</v>
-      </c>
-      <c r="BD35" s="3">
         <v>45806.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-05-29.xlsx
+++ b/jogos_2025-05-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="153">
   <si>
     <t>Date</t>
   </si>
@@ -232,10 +232,16 @@
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
@@ -244,21 +250,18 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Turkey 1. Lig</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
@@ -283,63 +286,66 @@
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
+    <t>HB</t>
+  </si>
+  <si>
     <t>Vestri</t>
   </si>
   <si>
-    <t>HB</t>
+    <t>LASK Linz</t>
   </si>
   <si>
     <t>Telavi</t>
   </si>
   <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Wisła Płock</t>
+  </si>
+  <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Wisła Płock</t>
-  </si>
-  <si>
     <t>Brann</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
   </si>
   <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Ghazl El Mehalla</t>
+  </si>
+  <si>
     <t>Masr</t>
   </si>
   <si>
     <t>Al Ittihad</t>
   </si>
   <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
     <t>El Geish</t>
   </si>
   <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Ghazl El Mehalla</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Cremonese</t>
   </si>
   <si>
@@ -352,18 +358,18 @@
     <t>Olimpia</t>
   </si>
   <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
     <t>Peñarol</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
+    <t>Racing Club</t>
   </si>
   <si>
     <t>Colo-Colo</t>
   </si>
   <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
     <t>Ferroviária</t>
   </si>
   <si>
@@ -373,63 +379,66 @@
     <t>Gareji</t>
   </si>
   <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Víkingur</t>
+    <t>Rapid Wien</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Djurgården</t>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>FH</t>
   </si>
   <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>ÍA</t>
   </si>
   <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Kolkheti Poti</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
     <t>Smouha SC</t>
   </si>
   <si>
     <t>ENPPI</t>
   </si>
   <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Bandırmaspor</t>
+  </si>
+  <si>
     <t>Coca-Cola</t>
   </si>
   <si>
-    <t>Bandırmaspor</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
-    <t>Kolkheti Poti</t>
-  </si>
-  <si>
     <t>Spezia</t>
   </si>
   <si>
@@ -442,16 +451,16 @@
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>CS Constantine</t>
+    <t>Fortaleza</t>
   </si>
   <si>
     <t>Atlético Bucaramanga</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
   </si>
   <si>
     <t>Botafogo SP</t>
@@ -827,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD31"/>
+  <dimension ref="A1:BD32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -1011,13 +1020,13 @@
         <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1032,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L2">
         <v>1.73</v>
@@ -1107,10 +1116,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL2">
         <v>1.21</v>
@@ -1181,13 +1190,13 @@
         <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1202,94 +1211,94 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="M3">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB3">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1331,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD3" s="3">
         <v>45806.3125</v>
@@ -1351,13 +1360,13 @@
         <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1372,94 +1381,94 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>2.22</v>
       </c>
       <c r="M4">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N4">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>1.79</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <v>17.75</v>
       </c>
       <c r="Q4">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="T4">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AA4">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC4">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD4">
+        <v>2.6</v>
+      </c>
+      <c r="AE4">
+        <v>1.44</v>
+      </c>
+      <c r="AF4">
+        <v>1.66</v>
+      </c>
+      <c r="AG4">
         <v>2.35</v>
       </c>
-      <c r="AE4">
+      <c r="AH4">
+        <v>4.7</v>
+      </c>
+      <c r="AI4">
+        <v>1.12</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL4">
+        <v>1.27</v>
+      </c>
+      <c r="AM4">
+        <v>1.23</v>
+      </c>
+      <c r="AN4">
         <v>1.52</v>
-      </c>
-      <c r="AF4">
-        <v>1.67</v>
-      </c>
-      <c r="AG4">
-        <v>2.08</v>
-      </c>
-      <c r="AH4">
-        <v>3.98</v>
-      </c>
-      <c r="AI4">
-        <v>1.21</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL4">
-        <v>1.17</v>
-      </c>
-      <c r="AM4">
-        <v>1.2</v>
-      </c>
-      <c r="AN4">
-        <v>1.11</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1471,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -1486,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="AW4">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX4">
         <v>0</v>
@@ -1501,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>3.25</v>
+        <v>1.79</v>
       </c>
       <c r="BC4">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="BD4" s="3">
         <v>45806.45833333334</v>
@@ -1521,13 +1530,13 @@
         <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1542,127 +1551,127 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L5">
-        <v>2.22</v>
+        <v>4.75</v>
       </c>
       <c r="M5">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="O5">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>17.75</v>
+        <v>13</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T5">
         <v>2.25</v>
       </c>
       <c r="U5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
         <v>1.14</v>
       </c>
       <c r="AA5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AB5">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC5">
+        <v>2.15</v>
+      </c>
+      <c r="AD5">
         <v>2.35</v>
       </c>
-      <c r="AD5">
-        <v>2.3</v>
-      </c>
       <c r="AE5">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AF5">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH5">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AI5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL5">
+        <v>2.23</v>
+      </c>
+      <c r="AM5">
         <v>1.2</v>
       </c>
-      <c r="AM5">
-        <v>1.23</v>
-      </c>
       <c r="AN5">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1671,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="BC5">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="BD5" s="3">
         <v>45806.45833333334</v>
@@ -1688,16 +1697,16 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
         <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1712,127 +1721,127 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1841,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" s="3">
         <v>45806.5</v>
@@ -1855,19 +1864,19 @@
         <v>45806</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1882,25 +1891,25 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1933,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1957,10 +1966,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2011,13 +2020,13 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD7" s="3">
-        <v>45806.54166666666</v>
+        <v>45806.5</v>
       </c>
     </row>
     <row r="8" spans="1:56">
@@ -2028,16 +2037,16 @@
         <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2052,127 +2061,127 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L8">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="M8">
-        <v>3.69</v>
+        <v>3.28</v>
       </c>
       <c r="N8">
-        <v>4.26</v>
+        <v>2.49</v>
       </c>
       <c r="O8">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="P8">
         <v>8.5</v>
       </c>
       <c r="Q8">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA8">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB8">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AD8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AI8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL8">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AM8">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AN8">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2181,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="BC8">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="BD8" s="3">
         <v>45806.54166666666</v>
@@ -2198,16 +2207,16 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
         <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2222,127 +2231,127 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L9">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="M9">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N9">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O9">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="U9">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA9">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AB9">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD9">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AE9">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH9">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AI9">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN9">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AS9">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AT9">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AU9">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AW9">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AX9">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AY9">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2351,10 +2360,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BC9">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BD9" s="3">
         <v>45806.54166666666</v>
@@ -2368,16 +2377,16 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2392,127 +2401,127 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L10">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="M10">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="N10">
-        <v>2.49</v>
+        <v>5.8</v>
       </c>
       <c r="O10">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="P10">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>1.73</v>
+        <v>3.75</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S10">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T10">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="U10">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AA10">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AB10">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AC10">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AD10">
         <v>3.2</v>
       </c>
       <c r="AE10">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="AG10">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI10">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL10">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AM10">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AN10">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2521,10 +2530,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="BC10">
-        <v>1.73</v>
+        <v>3.75</v>
       </c>
       <c r="BD10" s="3">
         <v>45806.54166666666</v>
@@ -2535,19 +2544,19 @@
         <v>45806</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2562,127 +2571,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="M11">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="N11">
-        <v>1.61</v>
+        <v>3.35</v>
       </c>
       <c r="O11">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="P11">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="Q11">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
+        <v>1.3</v>
+      </c>
+      <c r="S11">
+        <v>3.4</v>
+      </c>
+      <c r="T11">
+        <v>2.38</v>
+      </c>
+      <c r="U11">
+        <v>1.53</v>
+      </c>
+      <c r="V11">
+        <v>6</v>
+      </c>
+      <c r="W11">
+        <v>1.13</v>
+      </c>
+      <c r="X11">
+        <v>1.04</v>
+      </c>
+      <c r="Y11">
+        <v>10</v>
+      </c>
+      <c r="Z11">
         <v>1.2</v>
       </c>
-      <c r="S11">
-        <v>4.1</v>
-      </c>
-      <c r="T11">
-        <v>1.98</v>
-      </c>
-      <c r="U11">
-        <v>1.82</v>
-      </c>
-      <c r="V11">
-        <v>3.8</v>
-      </c>
-      <c r="W11">
-        <v>1.22</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>23</v>
-      </c>
-      <c r="Z11">
-        <v>1.04</v>
-      </c>
       <c r="AA11">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="AB11">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD11">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="AE11">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF11">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH11">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="AI11">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AJ11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL11">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="AM11">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AN11">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2691,13 +2700,13 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="BC11">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="BD11" s="3">
-        <v>45806.55208333334</v>
+        <v>45806.54166666666</v>
       </c>
     </row>
     <row r="12" spans="1:56">
@@ -2708,16 +2717,16 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2732,124 +2741,124 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L12">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="M12">
-        <v>3.55</v>
+        <v>3.73</v>
       </c>
       <c r="N12">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O12">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="P12">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Q12">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
         <v>1.25</v>
       </c>
       <c r="S12">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="U12">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="V12">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="W12">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Z12">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AA12">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AB12">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AC12">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AD12">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE12">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG12">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH12">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AI12">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AJ12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL12">
+        <v>1.21</v>
+      </c>
+      <c r="AM12">
         <v>1.25</v>
       </c>
-      <c r="AM12">
-        <v>1.26</v>
-      </c>
       <c r="AN12">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AT12">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY12">
         <v>1.82</v>
@@ -2861,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="BC12">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" s="3">
         <v>45806.55208333334</v>
@@ -2878,16 +2887,16 @@
         <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2902,127 +2911,127 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L13">
-        <v>1.3</v>
+        <v>2.48</v>
       </c>
       <c r="M13">
-        <v>5.2</v>
+        <v>3.63</v>
       </c>
       <c r="N13">
-        <v>6.6</v>
+        <v>2.37</v>
       </c>
       <c r="O13">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="P13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q13">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="R13">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S13">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="U13">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="V13">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="W13">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Z13">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>5.28</v>
       </c>
       <c r="AB13">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC13">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AD13">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE13">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="AH13">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="AI13">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AJ13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL13">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AM13">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AN13">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3031,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="BC13">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="BD13" s="3">
         <v>45806.55208333334</v>
@@ -3048,16 +3057,16 @@
         <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3072,127 +3081,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L14">
-        <v>2.29</v>
+        <v>3.7</v>
       </c>
       <c r="M14">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="O14">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="P14">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="R14">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S14">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="U14">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="V14">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Z14">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AA14">
-        <v>5</v>
+        <v>6.34</v>
       </c>
       <c r="AB14">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC14">
-        <v>2.37</v>
+        <v>3.04</v>
       </c>
       <c r="AD14">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AE14">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF14">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AH14">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AI14">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AJ14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL14">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AM14">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN14">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AT14">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AY14">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3201,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="BC14">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="BD14" s="3">
         <v>45806.55208333334</v>
@@ -3215,19 +3224,19 @@
         <v>45806</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3242,127 +3251,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L15">
-        <v>2.2</v>
+        <v>1.31</v>
       </c>
       <c r="M15">
-        <v>3.41</v>
+        <v>5.3</v>
       </c>
       <c r="N15">
-        <v>2.69</v>
+        <v>6.8</v>
       </c>
       <c r="O15">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="P15">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q15">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="R15">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S15">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="T15">
-        <v>2.49</v>
+        <v>1.8</v>
       </c>
       <c r="U15">
+        <v>1.9</v>
+      </c>
+      <c r="V15">
+        <v>3.6</v>
+      </c>
+      <c r="W15">
+        <v>1.25</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>21</v>
+      </c>
+      <c r="Z15">
+        <v>1.06</v>
+      </c>
+      <c r="AA15">
+        <v>7</v>
+      </c>
+      <c r="AB15">
+        <v>1.31</v>
+      </c>
+      <c r="AC15">
+        <v>3.15</v>
+      </c>
+      <c r="AD15">
+        <v>1.78</v>
+      </c>
+      <c r="AE15">
+        <v>1.92</v>
+      </c>
+      <c r="AF15">
         <v>1.5</v>
       </c>
-      <c r="V15">
-        <v>5.7</v>
-      </c>
-      <c r="W15">
-        <v>1.12</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>12.5</v>
-      </c>
-      <c r="Z15">
-        <v>1.2</v>
-      </c>
-      <c r="AA15">
-        <v>4.16</v>
-      </c>
-      <c r="AB15">
-        <v>1.67</v>
-      </c>
-      <c r="AC15">
-        <v>2.1</v>
-      </c>
-      <c r="AD15">
-        <v>2.64</v>
-      </c>
-      <c r="AE15">
-        <v>1.44</v>
-      </c>
-      <c r="AF15">
-        <v>1.57</v>
-      </c>
       <c r="AG15">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH15">
-        <v>4.63</v>
+        <v>2.8</v>
       </c>
       <c r="AI15">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AJ15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL15">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AM15">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN15">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AQ15">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AR15">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AS15">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="AT15">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AU15">
-        <v>3.15</v>
+        <v>5.25</v>
       </c>
       <c r="AV15">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="AW15">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="AX15">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AY15">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3371,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="BC15">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="BD15" s="3">
-        <v>45806.5625</v>
+        <v>45806.55208333334</v>
       </c>
     </row>
     <row r="16" spans="1:56">
@@ -3385,19 +3394,19 @@
         <v>45806</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
         <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3412,127 +3421,127 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L16">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M16">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="O16">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="P16">
-        <v>5.25</v>
+        <v>12</v>
       </c>
       <c r="Q16">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="R16">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="T16">
-        <v>3.8</v>
+        <v>2.49</v>
       </c>
       <c r="U16">
+        <v>1.5</v>
+      </c>
+      <c r="V16">
+        <v>5.7</v>
+      </c>
+      <c r="W16">
+        <v>1.12</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>12.5</v>
+      </c>
+      <c r="Z16">
         <v>1.2</v>
       </c>
-      <c r="V16">
-        <v>11</v>
-      </c>
-      <c r="W16">
-        <v>1.02</v>
-      </c>
-      <c r="X16">
-        <v>1.11</v>
-      </c>
-      <c r="Y16">
-        <v>5.35</v>
-      </c>
-      <c r="Z16">
-        <v>1.61</v>
-      </c>
       <c r="AA16">
-        <v>2.15</v>
+        <v>4.16</v>
       </c>
       <c r="AB16">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC16">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="AD16">
-        <v>6.25</v>
+        <v>2.64</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AF16">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="AH16">
-        <v>11</v>
+        <v>4.63</v>
       </c>
       <c r="AI16">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AJ16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL16">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AM16">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AN16">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3541,13 +3550,13 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BC16">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="BD16" s="3">
-        <v>45806.58333333334</v>
+        <v>45806.5625</v>
       </c>
     </row>
     <row r="17" spans="1:56">
@@ -3558,16 +3567,16 @@
         <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3582,94 +3591,94 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L17">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M17">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="N17">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z17">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AA17">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO17">
         <v>-1</v>
@@ -3711,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD17" s="3">
         <v>45806.58333333334</v>
@@ -3728,16 +3737,16 @@
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3752,37 +3761,37 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L18">
-        <v>3.78</v>
+        <v>2.09</v>
       </c>
       <c r="M18">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="N18">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="P18">
         <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="R18">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S18">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="T18">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -3791,10 +3800,10 @@
         <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Y18">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="Z18">
         <v>1.77</v>
@@ -3803,43 +3812,43 @@
         <v>1.93</v>
       </c>
       <c r="AB18">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AC18">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AD18">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AE18">
         <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AG18">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH18">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AI18">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK18" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL18">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AM18">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AN18">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AO18">
         <v>-1</v>
@@ -3881,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="BC18">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="BD18" s="3">
         <v>45806.58333333334</v>
@@ -3901,13 +3910,13 @@
         <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3922,94 +3931,94 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L19">
+        <v>2.85</v>
+      </c>
+      <c r="M19">
+        <v>2.82</v>
+      </c>
+      <c r="N19">
+        <v>2.6</v>
+      </c>
+      <c r="O19">
+        <v>2.05</v>
+      </c>
+      <c r="P19">
+        <v>5.25</v>
+      </c>
+      <c r="Q19">
+        <v>2.35</v>
+      </c>
+      <c r="R19">
+        <v>1.6</v>
+      </c>
+      <c r="S19">
+        <v>2.15</v>
+      </c>
+      <c r="T19">
+        <v>4.1</v>
+      </c>
+      <c r="U19">
+        <v>1.21</v>
+      </c>
+      <c r="V19">
+        <v>13</v>
+      </c>
+      <c r="W19">
+        <v>1.02</v>
+      </c>
+      <c r="X19">
+        <v>1.11</v>
+      </c>
+      <c r="Y19">
+        <v>5.4</v>
+      </c>
+      <c r="Z19">
+        <v>1.6</v>
+      </c>
+      <c r="AA19">
+        <v>2.25</v>
+      </c>
+      <c r="AB19">
+        <v>2.92</v>
+      </c>
+      <c r="AC19">
+        <v>1.34</v>
+      </c>
+      <c r="AD19">
+        <v>6.25</v>
+      </c>
+      <c r="AE19">
+        <v>1.11</v>
+      </c>
+      <c r="AF19">
         <v>2.3</v>
       </c>
-      <c r="M19">
-        <v>3.48</v>
-      </c>
-      <c r="N19">
-        <v>2.9</v>
-      </c>
-      <c r="O19">
-        <v>1.85</v>
-      </c>
-      <c r="P19">
-        <v>12</v>
-      </c>
-      <c r="Q19">
-        <v>2.1</v>
-      </c>
-      <c r="R19">
-        <v>1.32</v>
-      </c>
-      <c r="S19">
-        <v>3.24</v>
-      </c>
-      <c r="T19">
-        <v>2.61</v>
-      </c>
-      <c r="U19">
-        <v>1.46</v>
-      </c>
-      <c r="V19">
-        <v>6.3</v>
-      </c>
-      <c r="W19">
-        <v>1.06</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>10.4</v>
-      </c>
-      <c r="Z19">
-        <v>1.23</v>
-      </c>
-      <c r="AA19">
-        <v>3.92</v>
-      </c>
-      <c r="AB19">
-        <v>1.76</v>
-      </c>
-      <c r="AC19">
-        <v>2.03</v>
-      </c>
-      <c r="AD19">
-        <v>2.85</v>
-      </c>
-      <c r="AE19">
-        <v>1.39</v>
-      </c>
-      <c r="AF19">
+      <c r="AG19">
         <v>1.6</v>
       </c>
-      <c r="AG19">
-        <v>2.27</v>
-      </c>
       <c r="AH19">
-        <v>5.17</v>
+        <v>11</v>
       </c>
       <c r="AI19">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AJ19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AM19">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AN19">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AO19">
         <v>-1</v>
@@ -4051,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BC19">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="BD19" s="3">
         <v>45806.58333333334</v>
@@ -4068,16 +4077,16 @@
         <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4092,127 +4101,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L20">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="M20">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="N20">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="O20">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="P20">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>3.2</v>
       </c>
       <c r="R20">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="S20">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="U20">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="V20">
-        <v>5.25</v>
+        <v>11</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>1.13</v>
+        <v>1.78</v>
       </c>
       <c r="AA20">
-        <v>4.5</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
-        <v>1.69</v>
+        <v>3.64</v>
       </c>
       <c r="AC20">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="AD20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AH20">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK20" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL20">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ20">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR20">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU20">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV20">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW20">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX20">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY20">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4221,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="BC20">
         <v>3.2</v>
@@ -4238,16 +4247,16 @@
         <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4262,127 +4271,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L21">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="M21">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="N21">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="O21">
-        <v>1.93</v>
+        <v>1.37</v>
       </c>
       <c r="P21">
-        <v>4.5</v>
+        <v>16.25</v>
       </c>
       <c r="Q21">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="S21">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="T21">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="U21">
+        <v>1.52</v>
+      </c>
+      <c r="V21">
+        <v>5.25</v>
+      </c>
+      <c r="W21">
+        <v>1.11</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>13</v>
+      </c>
+      <c r="Z21">
         <v>1.15</v>
       </c>
-      <c r="V21">
-        <v>17</v>
-      </c>
-      <c r="W21">
-        <v>1.02</v>
-      </c>
-      <c r="X21">
-        <v>1.17</v>
-      </c>
-      <c r="Y21">
-        <v>4.5</v>
-      </c>
-      <c r="Z21">
+      <c r="AA21">
+        <v>4.33</v>
+      </c>
+      <c r="AB21">
+        <v>1.57</v>
+      </c>
+      <c r="AC21">
+        <v>2.15</v>
+      </c>
+      <c r="AD21">
+        <v>2.5</v>
+      </c>
+      <c r="AE21">
+        <v>1.44</v>
+      </c>
+      <c r="AF21">
         <v>1.77</v>
       </c>
-      <c r="AA21">
-        <v>1.93</v>
-      </c>
-      <c r="AB21">
-        <v>3.3</v>
-      </c>
-      <c r="AC21">
-        <v>1.29</v>
-      </c>
-      <c r="AD21">
-        <v>7</v>
-      </c>
-      <c r="AE21">
-        <v>1.07</v>
-      </c>
-      <c r="AF21">
-        <v>2.64</v>
-      </c>
       <c r="AG21">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AH21">
-        <v>17.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI21">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ21" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK21" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL21">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AM21">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AN21">
-        <v>1.65</v>
+        <v>2.67</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4391,10 +4400,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.93</v>
+        <v>1.37</v>
       </c>
       <c r="BC21">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="BD21" s="3">
         <v>45806.58333333334</v>
@@ -4408,16 +4417,16 @@
         <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
         <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4432,127 +4441,127 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L22">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="M22">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="N22">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AB22">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AC22">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ22" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK22" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4561,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" s="3">
         <v>45806.58333333334</v>
@@ -4575,19 +4584,19 @@
         <v>45806</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4602,127 +4611,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L23">
-        <v>3.02</v>
+        <v>3.78</v>
       </c>
       <c r="M23">
-        <v>3.47</v>
+        <v>2.41</v>
       </c>
       <c r="N23">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="O23">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="P23">
+        <v>4.5</v>
+      </c>
+      <c r="Q23">
+        <v>1.98</v>
+      </c>
+      <c r="R23">
+        <v>1.83</v>
+      </c>
+      <c r="S23">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>4.6</v>
+      </c>
+      <c r="U23">
+        <v>1.17</v>
+      </c>
+      <c r="V23">
         <v>9</v>
       </c>
-      <c r="Q23">
-        <v>2.1</v>
-      </c>
-      <c r="R23">
-        <v>1.38</v>
-      </c>
-      <c r="S23">
-        <v>2.8</v>
-      </c>
-      <c r="T23">
-        <v>2.65</v>
-      </c>
-      <c r="U23">
-        <v>1.41</v>
-      </c>
-      <c r="V23">
-        <v>6.75</v>
-      </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Y23">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="Z23">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="AA23">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB23">
-        <v>1.82</v>
+        <v>3.21</v>
       </c>
       <c r="AC23">
-        <v>1.92</v>
+        <v>1.3</v>
       </c>
       <c r="AD23">
-        <v>3.1</v>
+        <v>5.95</v>
       </c>
       <c r="AE23">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="AG23">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AH23">
-        <v>5.75</v>
+        <v>17</v>
       </c>
       <c r="AI23">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AJ23" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK23" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL23">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AM23">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AN23">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4731,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="BC23">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="BD23" s="3">
-        <v>45806.64583333334</v>
+        <v>45806.58333333334</v>
       </c>
     </row>
     <row r="24" spans="1:56">
@@ -4745,19 +4754,19 @@
         <v>45806</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F24" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4772,127 +4781,127 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L24">
-        <v>1.58</v>
+        <v>3.02</v>
       </c>
       <c r="M24">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="N24">
-        <v>5.2</v>
+        <v>2.22</v>
       </c>
       <c r="O24">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="P24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S24">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="T24">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="U24">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z24">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AA24">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AB24">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC24">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AD24">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AE24">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH24">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="AI24">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL24">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AM24">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AN24">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -4901,13 +4910,13 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="BC24">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="BD24" s="3">
-        <v>45806.66666666666</v>
+        <v>45806.64583333334</v>
       </c>
     </row>
     <row r="25" spans="1:56">
@@ -4915,19 +4924,19 @@
         <v>45806</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4942,94 +4951,94 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L25">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="M25">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N25">
-        <v>2.15</v>
+        <v>5.2</v>
       </c>
       <c r="O25">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="P25">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="R25">
+        <v>1.3</v>
+      </c>
+      <c r="S25">
+        <v>3.2</v>
+      </c>
+      <c r="T25">
+        <v>2.4</v>
+      </c>
+      <c r="U25">
+        <v>1.55</v>
+      </c>
+      <c r="V25">
+        <v>5.2</v>
+      </c>
+      <c r="W25">
+        <v>1.13</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>13</v>
+      </c>
+      <c r="Z25">
+        <v>1.22</v>
+      </c>
+      <c r="AA25">
+        <v>4.3</v>
+      </c>
+      <c r="AB25">
+        <v>1.65</v>
+      </c>
+      <c r="AC25">
+        <v>2.05</v>
+      </c>
+      <c r="AD25">
+        <v>2.62</v>
+      </c>
+      <c r="AE25">
+        <v>1.44</v>
+      </c>
+      <c r="AF25">
+        <v>1.7</v>
+      </c>
+      <c r="AG25">
+        <v>2</v>
+      </c>
+      <c r="AH25">
+        <v>4.75</v>
+      </c>
+      <c r="AI25">
         <v>1.15</v>
       </c>
-      <c r="S25">
-        <v>5.15</v>
-      </c>
-      <c r="T25">
-        <v>1.79</v>
-      </c>
-      <c r="U25">
-        <v>1.93</v>
-      </c>
-      <c r="V25">
-        <v>3.3</v>
-      </c>
-      <c r="W25">
-        <v>1.25</v>
-      </c>
-      <c r="X25">
-        <v>1</v>
-      </c>
-      <c r="Y25">
-        <v>21</v>
-      </c>
-      <c r="Z25">
-        <v>1.06</v>
-      </c>
-      <c r="AA25">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AB25">
-        <v>1.29</v>
-      </c>
-      <c r="AC25">
-        <v>3.6</v>
-      </c>
-      <c r="AD25">
-        <v>1.65</v>
-      </c>
-      <c r="AE25">
-        <v>2.05</v>
-      </c>
-      <c r="AF25">
-        <v>1.25</v>
-      </c>
-      <c r="AG25">
-        <v>3.55</v>
-      </c>
-      <c r="AH25">
-        <v>2.5</v>
-      </c>
-      <c r="AI25">
-        <v>1.46</v>
-      </c>
       <c r="AJ25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL25">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AM25">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AN25">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AO25">
         <v>-1</v>
@@ -5038,31 +5047,31 @@
         <v>0</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU25">
         <v>0</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5071,13 +5080,13 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="BC25">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="BD25" s="3">
-        <v>45806.67708333334</v>
+        <v>45806.66666666666</v>
       </c>
     </row>
     <row r="26" spans="1:56">
@@ -5085,19 +5094,19 @@
         <v>45806</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5112,40 +5121,40 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L26">
-        <v>1.14</v>
+        <v>2.33</v>
       </c>
       <c r="M26">
-        <v>6.9</v>
+        <v>3.97</v>
       </c>
       <c r="N26">
-        <v>9.800000000000001</v>
+        <v>2.39</v>
       </c>
       <c r="O26">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="P26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q26">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="R26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S26">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T26">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="U26">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="V26">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="W26">
         <v>1.29</v>
@@ -5157,83 +5166,83 @@
         <v>29</v>
       </c>
       <c r="Z26">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AA26">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC26">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="AD26">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE26">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AH26">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AI26">
         <v>1.48</v>
       </c>
       <c r="AJ26" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK26" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL26">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AM26">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AN26">
-        <v>4.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ26">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AR26">
+        <v>1.27</v>
+      </c>
+      <c r="AS26">
+        <v>1.42</v>
+      </c>
+      <c r="AT26">
+        <v>1.65</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>5</v>
+      </c>
+      <c r="AW26">
+        <v>3.58</v>
+      </c>
+      <c r="AX26">
+        <v>2.67</v>
+      </c>
+      <c r="AY26">
         <v>2.1</v>
       </c>
-      <c r="AS26">
-        <v>2.65</v>
-      </c>
-      <c r="AT26">
-        <v>3.45</v>
-      </c>
-      <c r="AU26">
-        <v>2.65</v>
-      </c>
-      <c r="AV26">
-        <v>2</v>
-      </c>
-      <c r="AW26">
-        <v>1.63</v>
-      </c>
-      <c r="AX26">
-        <v>1.41</v>
-      </c>
-      <c r="AY26">
-        <v>1.25</v>
-      </c>
       <c r="AZ26">
         <v>0</v>
       </c>
@@ -5241,13 +5250,13 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="BC26">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="BD26" s="3">
-        <v>45806.79166666666</v>
+        <v>45806.67708333334</v>
       </c>
     </row>
     <row r="27" spans="1:56">
@@ -5258,16 +5267,16 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5282,127 +5291,127 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L27">
-        <v>1.97</v>
+        <v>1.14</v>
       </c>
       <c r="M27">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="N27">
-        <v>3.74</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O27">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="P27">
-        <v>6.25</v>
+        <v>23</v>
       </c>
       <c r="Q27">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="R27">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="S27">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="U27">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="V27">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="X27">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>6.5</v>
+        <v>29</v>
       </c>
       <c r="Z27">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AA27">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="AB27">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AC27">
-        <v>1.5</v>
+        <v>3.33</v>
       </c>
       <c r="AD27">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="AE27">
-        <v>1.17</v>
+        <v>1.94</v>
       </c>
       <c r="AF27">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AH27">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="AI27">
+        <v>1.48</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL27">
         <v>1.04</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL27">
-        <v>1.25</v>
-      </c>
       <c r="AM27">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AN27">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AQ27">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AR27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AS27">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AT27">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AU27">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AV27">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AW27">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AX27">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AY27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5411,10 +5420,10 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="BC27">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="BD27" s="3">
         <v>45806.79166666666</v>
@@ -5428,16 +5437,16 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5452,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -5527,10 +5536,10 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK28" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5595,19 +5604,19 @@
         <v>45806</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -5622,127 +5631,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L29">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="M29">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N29">
-        <v>2.41</v>
+        <v>3.74</v>
       </c>
       <c r="O29">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="P29">
-        <v>9.25</v>
+        <v>6.25</v>
       </c>
       <c r="Q29">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
+        <v>1.53</v>
+      </c>
+      <c r="S29">
+        <v>2.38</v>
+      </c>
+      <c r="T29">
+        <v>3.75</v>
+      </c>
+      <c r="U29">
+        <v>1.25</v>
+      </c>
+      <c r="V29">
+        <v>11</v>
+      </c>
+      <c r="W29">
+        <v>1.05</v>
+      </c>
+      <c r="X29">
+        <v>1.1</v>
+      </c>
+      <c r="Y29">
+        <v>6.5</v>
+      </c>
+      <c r="Z29">
+        <v>1.5</v>
+      </c>
+      <c r="AA29">
+        <v>2.5</v>
+      </c>
+      <c r="AB29">
+        <v>2.3</v>
+      </c>
+      <c r="AC29">
+        <v>1.5</v>
+      </c>
+      <c r="AD29">
+        <v>5</v>
+      </c>
+      <c r="AE29">
+        <v>1.17</v>
+      </c>
+      <c r="AF29">
+        <v>2.2</v>
+      </c>
+      <c r="AG29">
+        <v>1.62</v>
+      </c>
+      <c r="AH29">
+        <v>10</v>
+      </c>
+      <c r="AI29">
+        <v>1.04</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL29">
+        <v>1.25</v>
+      </c>
+      <c r="AM29">
         <v>1.36</v>
       </c>
-      <c r="S29">
-        <v>3</v>
-      </c>
-      <c r="T29">
-        <v>2.75</v>
-      </c>
-      <c r="U29">
-        <v>1.4</v>
-      </c>
-      <c r="V29">
-        <v>7</v>
-      </c>
-      <c r="W29">
-        <v>1.1</v>
-      </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>10.2</v>
-      </c>
-      <c r="Z29">
-        <v>1.24</v>
-      </c>
-      <c r="AA29">
-        <v>3.48</v>
-      </c>
-      <c r="AB29">
-        <v>1.85</v>
-      </c>
-      <c r="AC29">
-        <v>1.85</v>
-      </c>
-      <c r="AD29">
-        <v>3.12</v>
-      </c>
-      <c r="AE29">
-        <v>1.29</v>
-      </c>
-      <c r="AF29">
+      <c r="AN29">
         <v>1.7</v>
-      </c>
-      <c r="AG29">
-        <v>2.05</v>
-      </c>
-      <c r="AH29">
-        <v>6.1</v>
-      </c>
-      <c r="AI29">
-        <v>1.06</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK29" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL29">
-        <v>1.5</v>
-      </c>
-      <c r="AM29">
-        <v>1.3</v>
-      </c>
-      <c r="AN29">
-        <v>1.44</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AR29">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AS29">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AT29">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="AU29">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="AV29">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AW29">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AX29">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AY29">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5751,13 +5760,13 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="BC29">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="BD29" s="3">
-        <v>45806.89583333334</v>
+        <v>45806.79166666666</v>
       </c>
     </row>
     <row r="30" spans="1:56">
@@ -5768,16 +5777,16 @@
         <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5792,7 +5801,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L30">
         <v>1.78</v>
@@ -5867,10 +5876,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AK30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL30">
         <v>1.22</v>
@@ -5935,19 +5944,19 @@
         <v>45806</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -5962,141 +5971,311 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L31">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="M31">
         <v>3.3</v>
       </c>
       <c r="N31">
-        <v>4.64</v>
+        <v>2.41</v>
       </c>
       <c r="O31">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="P31">
-        <v>6.75</v>
+        <v>9.25</v>
       </c>
       <c r="Q31">
+        <v>1.83</v>
+      </c>
+      <c r="R31">
+        <v>1.36</v>
+      </c>
+      <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="T31">
         <v>2.75</v>
       </c>
-      <c r="R31">
-        <v>1.53</v>
-      </c>
-      <c r="S31">
-        <v>2.34</v>
-      </c>
-      <c r="T31">
-        <v>3.5</v>
-      </c>
       <c r="U31">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
         <v>1.01</v>
       </c>
-      <c r="X31">
-        <v>1.11</v>
-      </c>
       <c r="Y31">
-        <v>6.5</v>
+        <v>10.2</v>
       </c>
       <c r="Z31">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AA31">
-        <v>2.45</v>
+        <v>3.48</v>
       </c>
       <c r="AB31">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC31">
+        <v>1.85</v>
+      </c>
+      <c r="AD31">
+        <v>3.12</v>
+      </c>
+      <c r="AE31">
+        <v>1.29</v>
+      </c>
+      <c r="AF31">
+        <v>1.7</v>
+      </c>
+      <c r="AG31">
+        <v>2.05</v>
+      </c>
+      <c r="AH31">
+        <v>6.1</v>
+      </c>
+      <c r="AI31">
+        <v>1.06</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL31">
+        <v>1.5</v>
+      </c>
+      <c r="AM31">
+        <v>1.3</v>
+      </c>
+      <c r="AN31">
         <v>1.44</v>
-      </c>
-      <c r="AD31">
-        <v>5</v>
-      </c>
-      <c r="AE31">
-        <v>1.15</v>
-      </c>
-      <c r="AF31">
-        <v>2.15</v>
-      </c>
-      <c r="AG31">
-        <v>1.67</v>
-      </c>
-      <c r="AH31">
-        <v>12</v>
-      </c>
-      <c r="AI31">
-        <v>1.04</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL31">
-        <v>1.36</v>
-      </c>
-      <c r="AM31">
-        <v>1.31</v>
-      </c>
-      <c r="AN31">
-        <v>1.83</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
+        <v>1.29</v>
+      </c>
+      <c r="AQ31">
+        <v>1.5</v>
+      </c>
+      <c r="AR31">
+        <v>1.82</v>
+      </c>
+      <c r="AS31">
+        <v>2.3</v>
+      </c>
+      <c r="AT31">
+        <v>2.9</v>
+      </c>
+      <c r="AU31">
+        <v>3.15</v>
+      </c>
+      <c r="AV31">
+        <v>2.38</v>
+      </c>
+      <c r="AW31">
+        <v>1.86</v>
+      </c>
+      <c r="AX31">
+        <v>1.54</v>
+      </c>
+      <c r="AY31">
+        <v>1.34</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>2.1</v>
+      </c>
+      <c r="BC31">
+        <v>1.83</v>
+      </c>
+      <c r="BD31" s="3">
+        <v>45806.89583333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:56">
+      <c r="A32" s="2">
+        <v>45806</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" t="s">
+        <v>149</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32">
+        <v>1.81</v>
+      </c>
+      <c r="M32">
+        <v>3.13</v>
+      </c>
+      <c r="N32">
+        <v>4.1</v>
+      </c>
+      <c r="O32">
+        <v>1.65</v>
+      </c>
+      <c r="P32">
+        <v>6.75</v>
+      </c>
+      <c r="Q32">
+        <v>2.75</v>
+      </c>
+      <c r="R32">
+        <v>1.55</v>
+      </c>
+      <c r="S32">
+        <v>2.15</v>
+      </c>
+      <c r="T32">
+        <v>3.3</v>
+      </c>
+      <c r="U32">
+        <v>1.25</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>1.04</v>
+      </c>
+      <c r="X32">
+        <v>1.11</v>
+      </c>
+      <c r="Y32">
+        <v>6.5</v>
+      </c>
+      <c r="Z32">
+        <v>1.45</v>
+      </c>
+      <c r="AA32">
+        <v>2.5</v>
+      </c>
+      <c r="AB32">
+        <v>2.3</v>
+      </c>
+      <c r="AC32">
+        <v>1.5</v>
+      </c>
+      <c r="AD32">
+        <v>5</v>
+      </c>
+      <c r="AE32">
+        <v>1.15</v>
+      </c>
+      <c r="AF32">
+        <v>2.15</v>
+      </c>
+      <c r="AG32">
+        <v>1.57</v>
+      </c>
+      <c r="AH32">
+        <v>9.1</v>
+      </c>
+      <c r="AI32">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL32">
+        <v>1.36</v>
+      </c>
+      <c r="AM32">
+        <v>1.31</v>
+      </c>
+      <c r="AN32">
+        <v>1.83</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
         <v>1.32</v>
       </c>
-      <c r="AQ31">
+      <c r="AQ32">
         <v>1.56</v>
       </c>
-      <c r="AR31">
+      <c r="AR32">
         <v>1.9</v>
       </c>
-      <c r="AS31">
+      <c r="AS32">
         <v>2.4</v>
       </c>
-      <c r="AT31">
+      <c r="AT32">
         <v>3.15</v>
       </c>
-      <c r="AU31">
+      <c r="AU32">
         <v>3</v>
       </c>
-      <c r="AV31">
+      <c r="AV32">
         <v>2.23</v>
       </c>
-      <c r="AW31">
+      <c r="AW32">
         <v>1.77</v>
       </c>
-      <c r="AX31">
+      <c r="AX32">
         <v>1.49</v>
       </c>
-      <c r="AY31">
+      <c r="AY32">
         <v>1.3</v>
       </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
         <v>1.65</v>
       </c>
-      <c r="BC31">
+      <c r="BC32">
         <v>2.75</v>
       </c>
-      <c r="BD31" s="3">
+      <c r="BD32" s="3">
         <v>45806.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-05-29.xlsx
+++ b/jogos_2025-05-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -232,45 +232,42 @@
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Turkey 1. Lig</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Turkey 1. Lig</t>
-  </si>
-  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
     <t>South America Copa Libertadores</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
@@ -286,66 +283,66 @@
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
+    <t>Vestri</t>
+  </si>
+  <si>
     <t>HB</t>
   </si>
   <si>
-    <t>Vestri</t>
+    <t>Telavi</t>
   </si>
   <si>
     <t>LASK Linz</t>
   </si>
   <si>
-    <t>Telavi</t>
+    <t>Brann</t>
   </si>
   <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Brann</t>
+    <t>Afturelding</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Afturelding</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
+    <t>Masr</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>El Geish</t>
+  </si>
+  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
-    <t>Masr</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>El Geish</t>
-  </si>
-  <si>
     <t>Cremonese</t>
   </si>
   <si>
@@ -355,15 +352,12 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Peñarol</t>
+  </si>
+  <si>
     <t>Olimpia</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Peñarol</t>
-  </si>
-  <si>
     <t>Racing Club</t>
   </si>
   <si>
@@ -379,66 +373,66 @@
     <t>Gareji</t>
   </si>
   <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
     <t>Víkingur</t>
   </si>
   <si>
-    <t>Víkingur Reykjavík</t>
+    <t>Samgurali</t>
   </si>
   <si>
     <t>Rapid Wien</t>
   </si>
   <si>
-    <t>Samgurali</t>
+    <t>Molde</t>
   </si>
   <si>
     <t>Djurgården</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Molde</t>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>ÍA</t>
   </si>
   <si>
     <t>KA</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Bandırmaspor</t>
+  </si>
+  <si>
     <t>Kolkheti Poti</t>
   </si>
   <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Bandırmaspor</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
     <t>Spezia</t>
   </si>
   <si>
@@ -448,13 +442,10 @@
     <t>KR</t>
   </si>
   <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
     <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Vélez Sarsfield</t>
   </si>
   <si>
     <t>Fortaleza</t>
@@ -836,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD32"/>
+  <dimension ref="A1:BD31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -1020,13 +1011,13 @@
         <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1041,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L2">
         <v>1.73</v>
@@ -1116,10 +1107,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL2">
         <v>1.21</v>
@@ -1190,13 +1181,13 @@
         <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1211,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L3">
         <v>1.59</v>
@@ -1262,10 +1253,10 @@
         <v>3</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD3">
         <v>3.6</v>
@@ -1286,10 +1277,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL3">
         <v>1.24</v>
@@ -1360,13 +1351,13 @@
         <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1381,127 +1372,127 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L4">
-        <v>2.22</v>
+        <v>4.75</v>
       </c>
       <c r="M4">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="O4">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>17.75</v>
+        <v>13</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V4">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z4">
+        <v>1.15</v>
+      </c>
+      <c r="AA4">
+        <v>4.5</v>
+      </c>
+      <c r="AB4">
+        <v>1.57</v>
+      </c>
+      <c r="AC4">
+        <v>2.15</v>
+      </c>
+      <c r="AD4">
+        <v>2.35</v>
+      </c>
+      <c r="AE4">
+        <v>1.52</v>
+      </c>
+      <c r="AF4">
+        <v>1.63</v>
+      </c>
+      <c r="AG4">
+        <v>2.12</v>
+      </c>
+      <c r="AH4">
+        <v>4.57</v>
+      </c>
+      <c r="AI4">
+        <v>1.18</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL4">
+        <v>2.3</v>
+      </c>
+      <c r="AM4">
         <v>1.2</v>
       </c>
-      <c r="AA4">
-        <v>4</v>
-      </c>
-      <c r="AB4">
-        <v>1.53</v>
-      </c>
-      <c r="AC4">
-        <v>2.35</v>
-      </c>
-      <c r="AD4">
-        <v>2.6</v>
-      </c>
-      <c r="AE4">
-        <v>1.44</v>
-      </c>
-      <c r="AF4">
-        <v>1.66</v>
-      </c>
-      <c r="AG4">
-        <v>2.35</v>
-      </c>
-      <c r="AH4">
-        <v>4.7</v>
-      </c>
-      <c r="AI4">
-        <v>1.12</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL4">
-        <v>1.27</v>
-      </c>
-      <c r="AM4">
-        <v>1.23</v>
-      </c>
       <c r="AN4">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1510,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="BC4">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="BD4" s="3">
         <v>45806.45833333334</v>
@@ -1530,13 +1521,13 @@
         <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1551,127 +1542,127 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L5">
-        <v>4.75</v>
+        <v>2.22</v>
       </c>
       <c r="M5">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N5">
+        <v>2.7</v>
+      </c>
+      <c r="O5">
+        <v>1.79</v>
+      </c>
+      <c r="P5">
+        <v>17.75</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>1.3</v>
+      </c>
+      <c r="S5">
+        <v>3.3</v>
+      </c>
+      <c r="T5">
+        <v>2.55</v>
+      </c>
+      <c r="U5">
+        <v>1.5</v>
+      </c>
+      <c r="V5">
+        <v>5.5</v>
+      </c>
+      <c r="W5">
+        <v>1.11</v>
+      </c>
+      <c r="X5">
+        <v>1.04</v>
+      </c>
+      <c r="Y5">
+        <v>10</v>
+      </c>
+      <c r="Z5">
+        <v>1.22</v>
+      </c>
+      <c r="AA5">
+        <v>3.8</v>
+      </c>
+      <c r="AB5">
+        <v>1.65</v>
+      </c>
+      <c r="AC5">
+        <v>2</v>
+      </c>
+      <c r="AD5">
+        <v>2.7</v>
+      </c>
+      <c r="AE5">
+        <v>1.33</v>
+      </c>
+      <c r="AF5">
         <v>1.55</v>
       </c>
-      <c r="O5">
-        <v>3.25</v>
-      </c>
-      <c r="P5">
-        <v>13</v>
-      </c>
-      <c r="Q5">
-        <v>1.36</v>
-      </c>
-      <c r="R5">
-        <v>1.25</v>
-      </c>
-      <c r="S5">
-        <v>3.42</v>
-      </c>
-      <c r="T5">
-        <v>2.25</v>
-      </c>
-      <c r="U5">
+      <c r="AG5">
+        <v>2.2</v>
+      </c>
+      <c r="AH5">
+        <v>3.95</v>
+      </c>
+      <c r="AI5">
+        <v>1.22</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL5">
+        <v>1.3</v>
+      </c>
+      <c r="AM5">
+        <v>1.23</v>
+      </c>
+      <c r="AN5">
         <v>1.6</v>
-      </c>
-      <c r="V5">
-        <v>5.1</v>
-      </c>
-      <c r="W5">
-        <v>1.12</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>15.5</v>
-      </c>
-      <c r="Z5">
-        <v>1.14</v>
-      </c>
-      <c r="AA5">
-        <v>4.6</v>
-      </c>
-      <c r="AB5">
-        <v>1.57</v>
-      </c>
-      <c r="AC5">
-        <v>2.15</v>
-      </c>
-      <c r="AD5">
-        <v>2.35</v>
-      </c>
-      <c r="AE5">
-        <v>1.52</v>
-      </c>
-      <c r="AF5">
-        <v>1.67</v>
-      </c>
-      <c r="AG5">
-        <v>2.15</v>
-      </c>
-      <c r="AH5">
-        <v>4</v>
-      </c>
-      <c r="AI5">
-        <v>1.2</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL5">
-        <v>2.23</v>
-      </c>
-      <c r="AM5">
-        <v>1.2</v>
-      </c>
-      <c r="AN5">
-        <v>1.18</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR5">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AS5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT5">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU5">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV5">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AW5">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AX5">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY5">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1680,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>3.25</v>
+        <v>1.79</v>
       </c>
       <c r="BC5">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="BD5" s="3">
         <v>45806.45833333334</v>
@@ -1697,16 +1688,16 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
         <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1721,127 +1712,127 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L6">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="M6">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="O6">
-        <v>1.88</v>
+        <v>2.63</v>
       </c>
       <c r="P6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q6">
+        <v>1.57</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
         <v>2.05</v>
       </c>
-      <c r="R6">
-        <v>1.26</v>
-      </c>
-      <c r="S6">
-        <v>3.6</v>
-      </c>
-      <c r="T6">
-        <v>2.39</v>
-      </c>
-      <c r="U6">
-        <v>1.58</v>
-      </c>
-      <c r="V6">
-        <v>4.7</v>
-      </c>
-      <c r="W6">
-        <v>1.14</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
-        <v>12</v>
-      </c>
-      <c r="Z6">
-        <v>1.18</v>
-      </c>
-      <c r="AA6">
-        <v>4.33</v>
-      </c>
-      <c r="AB6">
-        <v>1.57</v>
-      </c>
       <c r="AC6">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AD6">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR6">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS6">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT6">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU6">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV6">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AW6">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY6">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1850,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.88</v>
+        <v>2.63</v>
       </c>
       <c r="BC6">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="BD6" s="3">
         <v>45806.5</v>
@@ -1867,16 +1858,16 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1891,127 +1882,127 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L7">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="M7">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N7">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="O7">
-        <v>2.63</v>
+        <v>1.88</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q7">
+        <v>2.05</v>
+      </c>
+      <c r="R7">
+        <v>1.26</v>
+      </c>
+      <c r="S7">
+        <v>3.6</v>
+      </c>
+      <c r="T7">
+        <v>2.39</v>
+      </c>
+      <c r="U7">
+        <v>1.58</v>
+      </c>
+      <c r="V7">
+        <v>4.7</v>
+      </c>
+      <c r="W7">
+        <v>1.14</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>12</v>
+      </c>
+      <c r="Z7">
+        <v>1.18</v>
+      </c>
+      <c r="AA7">
+        <v>4.33</v>
+      </c>
+      <c r="AB7">
         <v>1.57</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>1.9</v>
-      </c>
       <c r="AC7">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2020,10 +2011,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>2.63</v>
+        <v>1.88</v>
       </c>
       <c r="BC7">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="BD7" s="3">
         <v>45806.5</v>
@@ -2040,13 +2031,13 @@
         <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2061,67 +2052,67 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L8">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="M8">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="N8">
-        <v>2.49</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="P8">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Q8">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U8">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA8">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB8">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AC8">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD8">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AE8">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AF8">
         <v>1.62</v>
@@ -2130,58 +2121,58 @@
         <v>2.2</v>
       </c>
       <c r="AH8">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="AI8">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AJ8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL8">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AM8">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AN8">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AR8">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AS8">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AT8">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AU8">
-        <v>3.55</v>
+        <v>4.55</v>
       </c>
       <c r="AV8">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AW8">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AX8">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AY8">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2190,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="BC8">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="BD8" s="3">
         <v>45806.54166666666</v>
@@ -2213,10 +2204,10 @@
         <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2231,46 +2222,46 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L9">
-        <v>1.79</v>
+        <v>2.42</v>
       </c>
       <c r="M9">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>2.49</v>
       </c>
       <c r="O9">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="P9">
         <v>8.5</v>
       </c>
       <c r="Q9">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="R9">
         <v>1.33</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T9">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V9">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -2279,79 +2270,79 @@
         <v>1.28</v>
       </c>
       <c r="AA9">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AD9">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AE9">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH9">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AI9">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL9">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AM9">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AN9">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ9">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AR9">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AS9">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AT9">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV9">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AW9">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AX9">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AY9">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2360,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="BC9">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="BD9" s="3">
         <v>45806.54166666666</v>
@@ -2380,13 +2371,13 @@
         <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2401,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L10">
         <v>1.51</v>
@@ -2452,10 +2443,10 @@
         <v>3.3</v>
       </c>
       <c r="AB10">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC10">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD10">
         <v>3.2</v>
@@ -2476,10 +2467,10 @@
         <v>1.08</v>
       </c>
       <c r="AJ10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL10">
         <v>1.08</v>
@@ -2550,13 +2541,13 @@
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2571,127 +2562,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L11">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="M11">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N11">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O11">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="P11">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R11">
         <v>1.3</v>
       </c>
       <c r="S11">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="T11">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="U11">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W11">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA11">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AB11">
+        <v>1.77</v>
+      </c>
+      <c r="AC11">
+        <v>1.93</v>
+      </c>
+      <c r="AD11">
+        <v>2.95</v>
+      </c>
+      <c r="AE11">
+        <v>1.34</v>
+      </c>
+      <c r="AF11">
         <v>1.6</v>
       </c>
-      <c r="AC11">
-        <v>2.1</v>
-      </c>
-      <c r="AD11">
-        <v>2.55</v>
-      </c>
-      <c r="AE11">
-        <v>1.5</v>
-      </c>
-      <c r="AF11">
-        <v>1.62</v>
-      </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AI11">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN11">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AQ11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AR11">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AS11">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AT11">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="AU11">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="AV11">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AW11">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AX11">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AY11">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2700,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BC11">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BD11" s="3">
         <v>45806.54166666666</v>
@@ -2717,16 +2708,16 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2741,127 +2732,127 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L12">
-        <v>1.97</v>
+        <v>3.7</v>
       </c>
       <c r="M12">
-        <v>3.73</v>
+        <v>4.1</v>
       </c>
       <c r="N12">
-        <v>3.09</v>
+        <v>1.7</v>
       </c>
       <c r="O12">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="P12">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="R12">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S12">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T12">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="U12">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="V12">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z12">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6.36</v>
       </c>
       <c r="AB12">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AC12">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="AD12">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AE12">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF12">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG12">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AH12">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="AI12">
+        <v>1.35</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL12">
         <v>1.22</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL12">
-        <v>1.21</v>
-      </c>
       <c r="AM12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN12">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AQ12">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AS12">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AT12">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AU12">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AV12">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AW12">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="AX12">
         <v>2.25</v>
       </c>
       <c r="AY12">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2870,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="BC12">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="BD12" s="3">
         <v>45806.55208333334</v>
@@ -2887,16 +2878,16 @@
         <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2911,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L13">
         <v>2.48</v>
@@ -2932,34 +2923,34 @@
         <v>1.88</v>
       </c>
       <c r="R13">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="U13">
         <v>1.68</v>
       </c>
       <c r="V13">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA13">
-        <v>5.28</v>
+        <v>5.5</v>
       </c>
       <c r="AB13">
         <v>1.42</v>
@@ -2974,31 +2965,31 @@
         <v>1.65</v>
       </c>
       <c r="AF13">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AG13">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AH13">
-        <v>3.52</v>
+        <v>3.78</v>
       </c>
       <c r="AI13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL13">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AM13">
         <v>1.26</v>
       </c>
       <c r="AN13">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AO13">
         <v>-1</v>
@@ -3007,31 +2998,31 @@
         <v>1.09</v>
       </c>
       <c r="AQ13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AR13">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AS13">
         <v>1.6</v>
       </c>
       <c r="AT13">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AU13">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="AV13">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AW13">
         <v>2.92</v>
       </c>
       <c r="AX13">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AY13">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3057,16 +3048,16 @@
         <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3081,127 +3072,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L14">
+        <v>1.31</v>
+      </c>
+      <c r="M14">
+        <v>5.3</v>
+      </c>
+      <c r="N14">
+        <v>6.8</v>
+      </c>
+      <c r="O14">
+        <v>1.36</v>
+      </c>
+      <c r="P14">
+        <v>19</v>
+      </c>
+      <c r="Q14">
+        <v>3.2</v>
+      </c>
+      <c r="R14">
+        <v>1.19</v>
+      </c>
+      <c r="S14">
+        <v>4.33</v>
+      </c>
+      <c r="T14">
+        <v>1.85</v>
+      </c>
+      <c r="U14">
+        <v>1.85</v>
+      </c>
+      <c r="V14">
         <v>3.7</v>
       </c>
-      <c r="M14">
-        <v>4.1</v>
-      </c>
-      <c r="N14">
-        <v>1.7</v>
-      </c>
-      <c r="O14">
-        <v>2.63</v>
-      </c>
-      <c r="P14">
-        <v>17.5</v>
-      </c>
-      <c r="Q14">
-        <v>1.44</v>
-      </c>
-      <c r="R14">
-        <v>1.15</v>
-      </c>
-      <c r="S14">
-        <v>4.1</v>
-      </c>
-      <c r="T14">
-        <v>1.93</v>
-      </c>
-      <c r="U14">
-        <v>1.81</v>
-      </c>
-      <c r="V14">
-        <v>3.92</v>
-      </c>
       <c r="W14">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z14">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AA14">
-        <v>6.34</v>
+        <v>6.5</v>
       </c>
       <c r="AB14">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC14">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AD14">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE14">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF14">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AG14">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH14">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AI14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AJ14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL14">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="AM14">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN14">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AQ14">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AR14">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AS14">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AT14">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AU14">
-        <v>5.7</v>
+        <v>5.45</v>
       </c>
       <c r="AV14">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AW14">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="AX14">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AY14">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3210,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>2.63</v>
+        <v>1.36</v>
       </c>
       <c r="BC14">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="BD14" s="3">
         <v>45806.55208333334</v>
@@ -3227,16 +3218,16 @@
         <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3251,127 +3242,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L15">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="M15">
-        <v>5.3</v>
+        <v>3.73</v>
       </c>
       <c r="N15">
-        <v>6.8</v>
+        <v>3.09</v>
       </c>
       <c r="O15">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="P15">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Q15">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S15">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="T15">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U15">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="V15">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="W15">
+        <v>1.15</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>14</v>
+      </c>
+      <c r="Z15">
+        <v>1.12</v>
+      </c>
+      <c r="AA15">
+        <v>5</v>
+      </c>
+      <c r="AB15">
+        <v>1.47</v>
+      </c>
+      <c r="AC15">
+        <v>2.5</v>
+      </c>
+      <c r="AD15">
+        <v>2.15</v>
+      </c>
+      <c r="AE15">
+        <v>1.6</v>
+      </c>
+      <c r="AF15">
+        <v>1.47</v>
+      </c>
+      <c r="AG15">
+        <v>2.5</v>
+      </c>
+      <c r="AH15">
+        <v>3.7</v>
+      </c>
+      <c r="AI15">
+        <v>1.24</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL15">
         <v>1.25</v>
       </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>21</v>
-      </c>
-      <c r="Z15">
-        <v>1.06</v>
-      </c>
-      <c r="AA15">
-        <v>7</v>
-      </c>
-      <c r="AB15">
-        <v>1.31</v>
-      </c>
-      <c r="AC15">
-        <v>3.15</v>
-      </c>
-      <c r="AD15">
-        <v>1.78</v>
-      </c>
-      <c r="AE15">
-        <v>1.92</v>
-      </c>
-      <c r="AF15">
-        <v>1.5</v>
-      </c>
-      <c r="AG15">
-        <v>2.4</v>
-      </c>
-      <c r="AH15">
-        <v>2.8</v>
-      </c>
-      <c r="AI15">
-        <v>1.37</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL15">
-        <v>1.11</v>
-      </c>
       <c r="AM15">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AN15">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AQ15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AR15">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS15">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AT15">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AU15">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AV15">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="AW15">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AX15">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AY15">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3380,10 +3371,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="BC15">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="BD15" s="3">
         <v>45806.55208333334</v>
@@ -3400,13 +3391,13 @@
         <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3421,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L16">
         <v>2.2</v>
@@ -3496,10 +3487,10 @@
         <v>1.17</v>
       </c>
       <c r="AJ16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL16">
         <v>1.36</v>
@@ -3567,16 +3558,16 @@
         <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3591,127 +3582,127 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L17">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="M17">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
-        <v>8.5</v>
+        <v>16.25</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="S17">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="T17">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="U17">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="V17">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>9.1</v>
+        <v>12.5</v>
       </c>
       <c r="Z17">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AA17">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AB17">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AC17">
+        <v>2.15</v>
+      </c>
+      <c r="AD17">
+        <v>2.53</v>
+      </c>
+      <c r="AE17">
+        <v>1.47</v>
+      </c>
+      <c r="AF17">
         <v>1.8</v>
       </c>
-      <c r="AD17">
-        <v>3.7</v>
-      </c>
-      <c r="AE17">
-        <v>1.23</v>
-      </c>
-      <c r="AF17">
-        <v>1.93</v>
-      </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>7.3</v>
+        <v>4.88</v>
       </c>
       <c r="AI17">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK17" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL17">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AM17">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN17">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3720,10 +3711,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="BC17">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BD17" s="3">
         <v>45806.58333333334</v>
@@ -3737,16 +3728,16 @@
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3761,127 +3752,127 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L18">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="M18">
-        <v>2.62</v>
+        <v>3.48</v>
       </c>
       <c r="N18">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="Q18">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="S18">
-        <v>1.97</v>
+        <v>3.24</v>
       </c>
       <c r="T18">
-        <v>4.8</v>
+        <v>2.61</v>
       </c>
       <c r="U18">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>10.4</v>
+      </c>
+      <c r="Z18">
+        <v>1.23</v>
+      </c>
+      <c r="AA18">
+        <v>3.92</v>
+      </c>
+      <c r="AB18">
+        <v>1.76</v>
+      </c>
+      <c r="AC18">
+        <v>2.03</v>
+      </c>
+      <c r="AD18">
+        <v>2.85</v>
+      </c>
+      <c r="AE18">
+        <v>1.39</v>
+      </c>
+      <c r="AF18">
+        <v>1.6</v>
+      </c>
+      <c r="AG18">
+        <v>2.27</v>
+      </c>
+      <c r="AH18">
+        <v>5.17</v>
+      </c>
+      <c r="AI18">
         <v>1.14</v>
       </c>
-      <c r="Y18">
-        <v>4.3</v>
-      </c>
-      <c r="Z18">
-        <v>1.77</v>
-      </c>
-      <c r="AA18">
-        <v>1.93</v>
-      </c>
-      <c r="AB18">
-        <v>3.48</v>
-      </c>
-      <c r="AC18">
-        <v>1.26</v>
-      </c>
-      <c r="AD18">
-        <v>7</v>
-      </c>
-      <c r="AE18">
-        <v>1.07</v>
-      </c>
-      <c r="AF18">
-        <v>2.7</v>
-      </c>
-      <c r="AG18">
+      <c r="AJ18" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL18">
         <v>1.4</v>
       </c>
-      <c r="AH18">
-        <v>18.5</v>
-      </c>
-      <c r="AI18">
-        <v>1</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL18">
-        <v>1.47</v>
-      </c>
       <c r="AM18">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AN18">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3890,10 +3881,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="BC18">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="BD18" s="3">
         <v>45806.58333333334</v>
@@ -3907,16 +3898,16 @@
         <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
         <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3931,94 +3922,94 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L19">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="M19">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="P19">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q19">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="S19">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="T19">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="U19">
+        <v>1.33</v>
+      </c>
+      <c r="V19">
+        <v>7.5</v>
+      </c>
+      <c r="W19">
+        <v>1.06</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>9.1</v>
+      </c>
+      <c r="Z19">
+        <v>1.35</v>
+      </c>
+      <c r="AA19">
+        <v>3</v>
+      </c>
+      <c r="AB19">
+        <v>1.95</v>
+      </c>
+      <c r="AC19">
+        <v>1.7</v>
+      </c>
+      <c r="AD19">
+        <v>3.7</v>
+      </c>
+      <c r="AE19">
+        <v>1.23</v>
+      </c>
+      <c r="AF19">
+        <v>1.93</v>
+      </c>
+      <c r="AG19">
+        <v>1.83</v>
+      </c>
+      <c r="AH19">
+        <v>7.3</v>
+      </c>
+      <c r="AI19">
+        <v>1.06</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL19">
+        <v>1.23</v>
+      </c>
+      <c r="AM19">
         <v>1.21</v>
       </c>
-      <c r="V19">
-        <v>13</v>
-      </c>
-      <c r="W19">
-        <v>1.02</v>
-      </c>
-      <c r="X19">
-        <v>1.11</v>
-      </c>
-      <c r="Y19">
-        <v>5.4</v>
-      </c>
-      <c r="Z19">
-        <v>1.6</v>
-      </c>
-      <c r="AA19">
-        <v>2.25</v>
-      </c>
-      <c r="AB19">
-        <v>2.92</v>
-      </c>
-      <c r="AC19">
-        <v>1.34</v>
-      </c>
-      <c r="AD19">
-        <v>6.25</v>
-      </c>
-      <c r="AE19">
-        <v>1.11</v>
-      </c>
-      <c r="AF19">
-        <v>2.3</v>
-      </c>
-      <c r="AG19">
-        <v>1.6</v>
-      </c>
-      <c r="AH19">
-        <v>11</v>
-      </c>
-      <c r="AI19">
-        <v>1.03</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL19">
-        <v>1.42</v>
-      </c>
-      <c r="AM19">
-        <v>1.38</v>
-      </c>
       <c r="AN19">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="AO19">
         <v>-1</v>
@@ -4060,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="BC19">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="BD19" s="3">
         <v>45806.58333333334</v>
@@ -4077,16 +4068,16 @@
         <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4101,127 +4092,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L20">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="M20">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="N20">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="O20">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q20">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="R20">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="S20">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="T20">
+        <v>3.42</v>
+      </c>
+      <c r="U20">
+        <v>1.21</v>
+      </c>
+      <c r="V20">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W20">
+        <v>1.01</v>
+      </c>
+      <c r="X20">
+        <v>1.09</v>
+      </c>
+      <c r="Y20">
         <v>5.5</v>
       </c>
-      <c r="U20">
-        <v>1.13</v>
-      </c>
-      <c r="V20">
-        <v>11</v>
-      </c>
-      <c r="W20">
+      <c r="Z20">
+        <v>1.5</v>
+      </c>
+      <c r="AA20">
+        <v>2.4</v>
+      </c>
+      <c r="AB20">
+        <v>2.38</v>
+      </c>
+      <c r="AC20">
+        <v>1.38</v>
+      </c>
+      <c r="AD20">
+        <v>5.75</v>
+      </c>
+      <c r="AE20">
+        <v>1.12</v>
+      </c>
+      <c r="AF20">
+        <v>2.3</v>
+      </c>
+      <c r="AG20">
+        <v>1.7</v>
+      </c>
+      <c r="AH20">
+        <v>9</v>
+      </c>
+      <c r="AI20">
         <v>1.02</v>
       </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>1.78</v>
-      </c>
-      <c r="AA20">
-        <v>1.92</v>
-      </c>
-      <c r="AB20">
-        <v>3.64</v>
-      </c>
-      <c r="AC20">
-        <v>1.24</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>2.75</v>
-      </c>
-      <c r="AG20">
-        <v>1.4</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
       <c r="AJ20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4230,10 +4221,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BC20">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="BD20" s="3">
         <v>45806.58333333334</v>
@@ -4247,16 +4238,16 @@
         <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4271,127 +4262,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L21">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="M21">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="N21">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="O21">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="P21">
-        <v>16.25</v>
+        <v>4</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
       </c>
       <c r="R21">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="S21">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="T21">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="U21">
+        <v>1.15</v>
+      </c>
+      <c r="V21">
+        <v>10.5</v>
+      </c>
+      <c r="W21">
+        <v>1.02</v>
+      </c>
+      <c r="X21">
+        <v>1.22</v>
+      </c>
+      <c r="Y21">
+        <v>3.8</v>
+      </c>
+      <c r="Z21">
+        <v>1.78</v>
+      </c>
+      <c r="AA21">
+        <v>1.92</v>
+      </c>
+      <c r="AB21">
+        <v>3.64</v>
+      </c>
+      <c r="AC21">
+        <v>1.24</v>
+      </c>
+      <c r="AD21">
+        <v>7.5</v>
+      </c>
+      <c r="AE21">
+        <v>1.06</v>
+      </c>
+      <c r="AF21">
+        <v>2.62</v>
+      </c>
+      <c r="AG21">
+        <v>1.42</v>
+      </c>
+      <c r="AH21">
+        <v>20</v>
+      </c>
+      <c r="AI21">
+        <v>1.01</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL21">
+        <v>1.5</v>
+      </c>
+      <c r="AM21">
+        <v>1.49</v>
+      </c>
+      <c r="AN21">
         <v>1.52</v>
-      </c>
-      <c r="V21">
-        <v>5.25</v>
-      </c>
-      <c r="W21">
-        <v>1.11</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>13</v>
-      </c>
-      <c r="Z21">
-        <v>1.15</v>
-      </c>
-      <c r="AA21">
-        <v>4.33</v>
-      </c>
-      <c r="AB21">
-        <v>1.57</v>
-      </c>
-      <c r="AC21">
-        <v>2.15</v>
-      </c>
-      <c r="AD21">
-        <v>2.5</v>
-      </c>
-      <c r="AE21">
-        <v>1.44</v>
-      </c>
-      <c r="AF21">
-        <v>1.77</v>
-      </c>
-      <c r="AG21">
-        <v>2</v>
-      </c>
-      <c r="AH21">
-        <v>4.33</v>
-      </c>
-      <c r="AI21">
-        <v>1.18</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL21">
-        <v>1.12</v>
-      </c>
-      <c r="AM21">
-        <v>1.18</v>
-      </c>
-      <c r="AN21">
-        <v>2.67</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AQ21">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="AR21">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AS21">
-        <v>1.88</v>
+        <v>3.35</v>
       </c>
       <c r="AT21">
-        <v>2.38</v>
+        <v>4.75</v>
       </c>
       <c r="AU21">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="AV21">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="AW21">
-        <v>2.36</v>
+        <v>1.44</v>
       </c>
       <c r="AX21">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="AY21">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4400,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="BC21">
         <v>3.2</v>
@@ -4420,13 +4411,13 @@
         <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4441,127 +4432,127 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L22">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
       <c r="M22">
-        <v>3.48</v>
+        <v>2.41</v>
       </c>
       <c r="N22">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="O22">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="P22">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R22">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="S22">
-        <v>3.24</v>
+        <v>1.95</v>
       </c>
       <c r="T22">
-        <v>2.61</v>
+        <v>4.1</v>
       </c>
       <c r="U22">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="V22">
-        <v>6.3</v>
+        <v>15</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="Y22">
-        <v>10.4</v>
+        <v>4.33</v>
       </c>
       <c r="Z22">
-        <v>1.23</v>
+        <v>1.77</v>
       </c>
       <c r="AA22">
-        <v>3.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB22">
-        <v>1.76</v>
+        <v>3.21</v>
       </c>
       <c r="AC22">
-        <v>2.03</v>
+        <v>1.3</v>
       </c>
       <c r="AD22">
-        <v>2.85</v>
+        <v>5.55</v>
       </c>
       <c r="AE22">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="AG22">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AH22">
-        <v>5.17</v>
+        <v>14</v>
       </c>
       <c r="AI22">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AJ22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL22">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AM22">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AN22">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AR22">
-        <v>2.09</v>
+        <v>2.77</v>
       </c>
       <c r="AS22">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AT22">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="AU22">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="AV22">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AW22">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AX22">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AY22">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4570,10 +4561,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="BC22">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="BD22" s="3">
         <v>45806.58333333334</v>
@@ -4587,16 +4578,16 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4611,49 +4602,49 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L23">
-        <v>3.78</v>
+        <v>2.09</v>
       </c>
       <c r="M23">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="N23">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="O23">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="P23">
         <v>4.5</v>
       </c>
       <c r="Q23">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="R23">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T23">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U23">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Z23">
         <v>1.77</v>
@@ -4662,76 +4653,76 @@
         <v>1.93</v>
       </c>
       <c r="AB23">
-        <v>3.21</v>
+        <v>3.48</v>
       </c>
       <c r="AC23">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AD23">
-        <v>5.95</v>
+        <v>4.9</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AG23">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH23">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AI23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ23" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK23" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL23">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AM23">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AN23">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4740,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="BC23">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="BD23" s="3">
         <v>45806.58333333334</v>
@@ -4760,13 +4751,13 @@
         <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4781,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L24">
         <v>3.02</v>
@@ -4856,10 +4847,10 @@
         <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK24" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL24">
         <v>1.39</v>
@@ -4927,16 +4918,16 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4951,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L25">
         <v>1.46</v>
@@ -4981,25 +4972,25 @@
         <v>2.4</v>
       </c>
       <c r="U25">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V25">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z25">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AA25">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AB25">
         <v>1.65</v>
@@ -5008,43 +4999,43 @@
         <v>2.05</v>
       </c>
       <c r="AD25">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AE25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF25">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
         <v>2</v>
       </c>
       <c r="AH25">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AI25">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AJ25" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK25" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM25">
         <v>1.2</v>
       </c>
       <c r="AN25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ25">
         <v>1.22</v>
@@ -5053,25 +5044,25 @@
         <v>1.49</v>
       </c>
       <c r="AS25">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AT25">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW25">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AX25">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AY25">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5097,16 +5088,16 @@
         <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5121,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L26">
         <v>2.33</v>
@@ -5142,22 +5133,22 @@
         <v>1.83</v>
       </c>
       <c r="R26">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S26">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T26">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U26">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V26">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="W26">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -5166,10 +5157,10 @@
         <v>29</v>
       </c>
       <c r="Z26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="AB26">
         <v>1.27</v>
@@ -5184,31 +5175,31 @@
         <v>2.05</v>
       </c>
       <c r="AF26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AG26">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AH26">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AI26">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AJ26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL26">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AM26">
         <v>1.23</v>
       </c>
       <c r="AN26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AO26">
         <v>-1</v>
@@ -5220,7 +5211,7 @@
         <v>1.15</v>
       </c>
       <c r="AR26">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AS26">
         <v>1.42</v>
@@ -5232,13 +5223,13 @@
         <v>0</v>
       </c>
       <c r="AV26">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AW26">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AX26">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AY26">
         <v>2.1</v>
@@ -5270,13 +5261,13 @@
         <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5291,127 +5282,127 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L27">
-        <v>1.14</v>
+        <v>1.97</v>
       </c>
       <c r="M27">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="N27">
-        <v>9.800000000000001</v>
+        <v>3.74</v>
       </c>
       <c r="O27">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="P27">
-        <v>23</v>
+        <v>6.25</v>
       </c>
       <c r="Q27">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
+        <v>1.53</v>
+      </c>
+      <c r="S27">
+        <v>2.38</v>
+      </c>
+      <c r="T27">
+        <v>3.75</v>
+      </c>
+      <c r="U27">
+        <v>1.25</v>
+      </c>
+      <c r="V27">
+        <v>11</v>
+      </c>
+      <c r="W27">
+        <v>1.05</v>
+      </c>
+      <c r="X27">
+        <v>1.1</v>
+      </c>
+      <c r="Y27">
+        <v>6.5</v>
+      </c>
+      <c r="Z27">
+        <v>1.5</v>
+      </c>
+      <c r="AA27">
+        <v>2.5</v>
+      </c>
+      <c r="AB27">
+        <v>2.3</v>
+      </c>
+      <c r="AC27">
+        <v>1.5</v>
+      </c>
+      <c r="AD27">
+        <v>5</v>
+      </c>
+      <c r="AE27">
         <v>1.17</v>
       </c>
-      <c r="S27">
-        <v>5</v>
-      </c>
-      <c r="T27">
-        <v>1.8</v>
-      </c>
-      <c r="U27">
-        <v>1.91</v>
-      </c>
-      <c r="V27">
-        <v>3.5</v>
-      </c>
-      <c r="W27">
-        <v>1.29</v>
-      </c>
-      <c r="X27">
-        <v>1.01</v>
-      </c>
-      <c r="Y27">
-        <v>29</v>
-      </c>
-      <c r="Z27">
-        <v>1.08</v>
-      </c>
-      <c r="AA27">
-        <v>7.5</v>
-      </c>
-      <c r="AB27">
-        <v>1.3</v>
-      </c>
-      <c r="AC27">
-        <v>3.33</v>
-      </c>
-      <c r="AD27">
-        <v>1.76</v>
-      </c>
-      <c r="AE27">
-        <v>1.94</v>
-      </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH27">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="AI27">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="AJ27" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK27" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL27">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AM27">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AN27">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AQ27">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AR27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AS27">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AT27">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AU27">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AV27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AW27">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AX27">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AY27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5420,10 +5411,10 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="BC27">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="BD27" s="3">
         <v>45806.79166666666</v>
@@ -5437,16 +5428,16 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
         <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5461,127 +5452,127 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ28" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK28" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO28">
         <v>-1</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -5590,10 +5581,10 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BD28" s="3">
         <v>45806.79166666666</v>
@@ -5604,19 +5595,19 @@
         <v>45806</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
         <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -5631,127 +5622,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L29">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="M29">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="N29">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="O29">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="P29">
-        <v>6.25</v>
+        <v>8.25</v>
       </c>
       <c r="Q29">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R29">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S29">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="T29">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="U29">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="V29">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
+        <v>8.25</v>
+      </c>
+      <c r="Z29">
+        <v>1.33</v>
+      </c>
+      <c r="AA29">
+        <v>3.1</v>
+      </c>
+      <c r="AB29">
+        <v>1.94</v>
+      </c>
+      <c r="AC29">
+        <v>1.76</v>
+      </c>
+      <c r="AD29">
+        <v>3.4</v>
+      </c>
+      <c r="AE29">
+        <v>1.27</v>
+      </c>
+      <c r="AF29">
+        <v>1.85</v>
+      </c>
+      <c r="AG29">
+        <v>1.82</v>
+      </c>
+      <c r="AH29">
         <v>6.5</v>
       </c>
-      <c r="Z29">
-        <v>1.5</v>
-      </c>
-      <c r="AA29">
-        <v>2.5</v>
-      </c>
-      <c r="AB29">
-        <v>2.3</v>
-      </c>
-      <c r="AC29">
-        <v>1.5</v>
-      </c>
-      <c r="AD29">
-        <v>5</v>
-      </c>
-      <c r="AE29">
-        <v>1.17</v>
-      </c>
-      <c r="AF29">
-        <v>2.2</v>
-      </c>
-      <c r="AG29">
-        <v>1.62</v>
-      </c>
-      <c r="AH29">
-        <v>10</v>
-      </c>
       <c r="AI29">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AJ29" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK29" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM29">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN29">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AS29">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="AT29">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="AU29">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV29">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="AW29">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AX29">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AY29">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5760,13 +5751,13 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BC29">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BD29" s="3">
-        <v>45806.79166666666</v>
+        <v>45806.89583333334</v>
       </c>
     </row>
     <row r="30" spans="1:56">
@@ -5780,13 +5771,13 @@
         <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5801,127 +5792,127 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L30">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="M30">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="O30">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="P30">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="Q30">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="R30">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S30">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T30">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U30">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V30">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>10.2</v>
+      </c>
+      <c r="Z30">
+        <v>1.24</v>
+      </c>
+      <c r="AA30">
+        <v>3.48</v>
+      </c>
+      <c r="AB30">
+        <v>1.85</v>
+      </c>
+      <c r="AC30">
+        <v>1.85</v>
+      </c>
+      <c r="AD30">
+        <v>3.12</v>
+      </c>
+      <c r="AE30">
+        <v>1.29</v>
+      </c>
+      <c r="AF30">
+        <v>1.7</v>
+      </c>
+      <c r="AG30">
+        <v>2.05</v>
+      </c>
+      <c r="AH30">
+        <v>6.1</v>
+      </c>
+      <c r="AI30">
         <v>1.06</v>
       </c>
-      <c r="Y30">
-        <v>8.25</v>
-      </c>
-      <c r="Z30">
-        <v>1.33</v>
-      </c>
-      <c r="AA30">
-        <v>3.1</v>
-      </c>
-      <c r="AB30">
-        <v>1.94</v>
-      </c>
-      <c r="AC30">
-        <v>1.76</v>
-      </c>
-      <c r="AD30">
-        <v>3.4</v>
-      </c>
-      <c r="AE30">
-        <v>1.27</v>
-      </c>
-      <c r="AF30">
-        <v>1.85</v>
-      </c>
-      <c r="AG30">
-        <v>1.82</v>
-      </c>
-      <c r="AH30">
-        <v>6.5</v>
-      </c>
-      <c r="AI30">
-        <v>1.09</v>
-      </c>
       <c r="AJ30" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AK30" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AL30">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AM30">
         <v>1.3</v>
       </c>
       <c r="AN30">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AQ30">
         <v>1.5</v>
       </c>
       <c r="AR30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AS30">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AT30">
         <v>2.9</v>
       </c>
       <c r="AU30">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AV30">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AW30">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AX30">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AY30">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AZ30">
         <v>0</v>
@@ -5930,10 +5921,10 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="BC30">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="BD30" s="3">
         <v>45806.89583333334</v>
@@ -5944,154 +5935,154 @@
         <v>45806</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
         <v>148</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>151</v>
-      </c>
       <c r="L31">
-        <v>2.49</v>
+        <v>1.81</v>
       </c>
       <c r="M31">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N31">
-        <v>2.41</v>
+        <v>4.1</v>
       </c>
       <c r="O31">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="P31">
-        <v>9.25</v>
+        <v>6.75</v>
       </c>
       <c r="Q31">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="R31">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="T31">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U31">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W31">
+        <v>1.03</v>
+      </c>
+      <c r="X31">
         <v>1.1</v>
       </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
       <c r="Y31">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="Z31">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AA31">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AB31">
+        <v>2.3</v>
+      </c>
+      <c r="AC31">
+        <v>1.5</v>
+      </c>
+      <c r="AD31">
+        <v>5.44</v>
+      </c>
+      <c r="AE31">
+        <v>1.15</v>
+      </c>
+      <c r="AF31">
+        <v>2.25</v>
+      </c>
+      <c r="AG31">
+        <v>1.62</v>
+      </c>
+      <c r="AH31">
+        <v>9.1</v>
+      </c>
+      <c r="AI31">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL31">
+        <v>1.33</v>
+      </c>
+      <c r="AM31">
+        <v>1.31</v>
+      </c>
+      <c r="AN31">
         <v>1.85</v>
-      </c>
-      <c r="AC31">
-        <v>1.85</v>
-      </c>
-      <c r="AD31">
-        <v>3.12</v>
-      </c>
-      <c r="AE31">
-        <v>1.29</v>
-      </c>
-      <c r="AF31">
-        <v>1.7</v>
-      </c>
-      <c r="AG31">
-        <v>2.05</v>
-      </c>
-      <c r="AH31">
-        <v>6.1</v>
-      </c>
-      <c r="AI31">
-        <v>1.06</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL31">
-        <v>1.5</v>
-      </c>
-      <c r="AM31">
-        <v>1.3</v>
-      </c>
-      <c r="AN31">
-        <v>1.44</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR31">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AS31">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AT31">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="AU31">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="AV31">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AW31">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AX31">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AY31">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6100,182 +6091,12 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="BC31">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="BD31" s="3">
-        <v>45806.89583333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:56">
-      <c r="A32" s="2">
-        <v>45806</v>
-      </c>
-      <c r="B32" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" t="s">
-        <v>118</v>
-      </c>
-      <c r="F32" t="s">
-        <v>149</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
-        <v>151</v>
-      </c>
-      <c r="L32">
-        <v>1.81</v>
-      </c>
-      <c r="M32">
-        <v>3.13</v>
-      </c>
-      <c r="N32">
-        <v>4.1</v>
-      </c>
-      <c r="O32">
-        <v>1.65</v>
-      </c>
-      <c r="P32">
-        <v>6.75</v>
-      </c>
-      <c r="Q32">
-        <v>2.75</v>
-      </c>
-      <c r="R32">
-        <v>1.55</v>
-      </c>
-      <c r="S32">
-        <v>2.15</v>
-      </c>
-      <c r="T32">
-        <v>3.3</v>
-      </c>
-      <c r="U32">
-        <v>1.25</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>1.04</v>
-      </c>
-      <c r="X32">
-        <v>1.11</v>
-      </c>
-      <c r="Y32">
-        <v>6.5</v>
-      </c>
-      <c r="Z32">
-        <v>1.45</v>
-      </c>
-      <c r="AA32">
-        <v>2.5</v>
-      </c>
-      <c r="AB32">
-        <v>2.3</v>
-      </c>
-      <c r="AC32">
-        <v>1.5</v>
-      </c>
-      <c r="AD32">
-        <v>5</v>
-      </c>
-      <c r="AE32">
-        <v>1.15</v>
-      </c>
-      <c r="AF32">
-        <v>2.15</v>
-      </c>
-      <c r="AG32">
-        <v>1.57</v>
-      </c>
-      <c r="AH32">
-        <v>9.1</v>
-      </c>
-      <c r="AI32">
-        <v>1</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL32">
-        <v>1.36</v>
-      </c>
-      <c r="AM32">
-        <v>1.31</v>
-      </c>
-      <c r="AN32">
-        <v>1.83</v>
-      </c>
-      <c r="AO32">
-        <v>-1</v>
-      </c>
-      <c r="AP32">
-        <v>1.32</v>
-      </c>
-      <c r="AQ32">
-        <v>1.56</v>
-      </c>
-      <c r="AR32">
-        <v>1.9</v>
-      </c>
-      <c r="AS32">
-        <v>2.4</v>
-      </c>
-      <c r="AT32">
-        <v>3.15</v>
-      </c>
-      <c r="AU32">
-        <v>3</v>
-      </c>
-      <c r="AV32">
-        <v>2.23</v>
-      </c>
-      <c r="AW32">
-        <v>1.77</v>
-      </c>
-      <c r="AX32">
-        <v>1.49</v>
-      </c>
-      <c r="AY32">
-        <v>1.3</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>1.65</v>
-      </c>
-      <c r="BC32">
-        <v>2.75</v>
-      </c>
-      <c r="BD32" s="3">
         <v>45806.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-05-29.xlsx
+++ b/jogos_2025-05-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="167">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -232,12 +178,12 @@
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
@@ -253,15 +199,15 @@
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Turkey 1. Lig</t>
+  </si>
+  <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Turkey 1. Lig</t>
-  </si>
-  <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
@@ -283,12 +229,12 @@
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
+    <t>HB</t>
+  </si>
+  <si>
     <t>Vestri</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
     <t>Telavi</t>
   </si>
   <si>
@@ -298,51 +244,51 @@
     <t>Brann</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
     <t>Wisła Płock</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>El Geish</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Ghazl El Mehalla</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>El Geish</t>
-  </si>
-  <si>
-    <t>Ghazl El Mehalla</t>
-  </si>
-  <si>
     <t>Cremonese</t>
   </si>
   <si>
@@ -352,12 +298,12 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Olimpia</t>
+  </si>
+  <si>
     <t>Peñarol</t>
   </si>
   <si>
-    <t>Olimpia</t>
-  </si>
-  <si>
     <t>Racing Club</t>
   </si>
   <si>
@@ -373,12 +319,12 @@
     <t>Gareji</t>
   </si>
   <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
     <t>Samgurali</t>
   </si>
   <si>
@@ -388,51 +334,51 @@
     <t>Molde</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>ÍA</t>
+  </si>
+  <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Bandırmaspor</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Kolkheti Poti</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Mjøndalen</t>
   </si>
   <si>
-    <t>Bandırmaspor</t>
-  </si>
-  <si>
-    <t>Kolkheti Poti</t>
-  </si>
-  <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
     <t>Spezia</t>
   </si>
   <si>
@@ -442,12 +388,12 @@
     <t>KR</t>
   </si>
   <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
@@ -457,13 +403,118 @@
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>suspended</t>
-  </si>
-  <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['44', '60']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['5', '66', '90+1']</t>
+  </si>
+  <si>
+    <t>['-1', '-1', '-1']</t>
+  </si>
+  <si>
+    <t>['34', '89']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['63', '90+2']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['46', '91', '105']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['-1', '-1']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['3', '9', '11', '57']</t>
+  </si>
+  <si>
+    <t>['52', '53', '56', '82']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['11', '48', '72']</t>
+  </si>
+  <si>
+    <t>['45+2', '90+2']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['29', '35', '40', '90+5']</t>
+  </si>
+  <si>
+    <t>['34', '41']</t>
+  </si>
+  <si>
+    <t>['61', '90+5']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['45']</t>
+  </si>
+  <si>
+    <t>['6', '11', '34']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['45+5', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -827,10 +878,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD31"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -945,94 +996,40 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45806</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="L2">
         <v>1.73</v>
@@ -1107,93 +1104,39 @@
         <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="AK2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL2">
-        <v>1.21</v>
-      </c>
-      <c r="AM2">
-        <v>1.32</v>
-      </c>
-      <c r="AN2">
-        <v>1.87</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.41</v>
-      </c>
-      <c r="AQ2">
-        <v>1.77</v>
-      </c>
-      <c r="AR2">
-        <v>2.28</v>
-      </c>
-      <c r="AS2">
-        <v>3.08</v>
-      </c>
-      <c r="AT2">
-        <v>4.35</v>
-      </c>
-      <c r="AU2">
-        <v>2.52</v>
-      </c>
-      <c r="AV2">
-        <v>1.9</v>
-      </c>
-      <c r="AW2">
-        <v>1.5</v>
-      </c>
-      <c r="AX2">
-        <v>1.28</v>
-      </c>
-      <c r="AY2">
-        <v>1.17</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.66</v>
-      </c>
-      <c r="BC2">
-        <v>2.8</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>152</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45806.29166666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45806</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1202,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L3">
         <v>1.59</v>
@@ -1277,433 +1220,271 @@
         <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL3">
-        <v>1.24</v>
-      </c>
-      <c r="AM3">
-        <v>1.22</v>
-      </c>
-      <c r="AN3">
-        <v>1.85</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.53</v>
-      </c>
-      <c r="BC3">
-        <v>3</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>143</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45806.3125</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45806</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L4">
-        <v>4.75</v>
+        <v>2.22</v>
       </c>
       <c r="M4">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N4">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>1.79</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <v>17.75</v>
       </c>
       <c r="Q4">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="T4">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V4">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD4">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="AE4">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF4">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH4">
-        <v>4.57</v>
+        <v>3.95</v>
       </c>
       <c r="AI4">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="AK4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL4">
-        <v>2.3</v>
-      </c>
-      <c r="AM4">
-        <v>1.2</v>
-      </c>
-      <c r="AN4">
-        <v>1.17</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.29</v>
-      </c>
-      <c r="AQ4">
-        <v>1.47</v>
-      </c>
-      <c r="AR4">
-        <v>1.83</v>
-      </c>
-      <c r="AS4">
-        <v>2.2</v>
-      </c>
-      <c r="AT4">
-        <v>2.9</v>
-      </c>
-      <c r="AU4">
-        <v>3.3</v>
-      </c>
-      <c r="AV4">
-        <v>2.5</v>
-      </c>
-      <c r="AW4">
-        <v>1.91</v>
-      </c>
-      <c r="AX4">
-        <v>1.51</v>
-      </c>
-      <c r="AY4">
-        <v>1.36</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>3.25</v>
-      </c>
-      <c r="BC4">
-        <v>1.36</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>146</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45806.45833333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45806</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L5">
-        <v>2.22</v>
+        <v>4.75</v>
       </c>
       <c r="M5">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="O5">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>17.75</v>
+        <v>13</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
         <v>3.3</v>
       </c>
       <c r="T5">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U5">
         <v>1.5</v>
       </c>
       <c r="V5">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AA5">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB5">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC5">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD5">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AE5">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AF5">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AG5">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH5">
-        <v>3.95</v>
+        <v>4.97</v>
       </c>
       <c r="AI5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL5">
-        <v>1.3</v>
-      </c>
-      <c r="AM5">
-        <v>1.23</v>
-      </c>
-      <c r="AN5">
-        <v>1.6</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>1.82</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>1.98</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.79</v>
-      </c>
-      <c r="BC5">
-        <v>2</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>153</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45806.45833333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45806</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1712,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L6">
         <v>3.55</v>
@@ -1787,102 +1568,48 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="AK6" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2.63</v>
-      </c>
-      <c r="BC6">
-        <v>1.57</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>135</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45806.5</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45806</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
         <v>74</v>
       </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>92</v>
-      </c>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L7">
         <v>2.35</v>
@@ -1957,102 +1684,48 @@
         <v>1.2</v>
       </c>
       <c r="AJ7" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="AK7" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL7">
-        <v>1.44</v>
-      </c>
-      <c r="AM7">
-        <v>1.28</v>
-      </c>
-      <c r="AN7">
-        <v>1.61</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.25</v>
-      </c>
-      <c r="AQ7">
-        <v>1.47</v>
-      </c>
-      <c r="AR7">
-        <v>1.85</v>
-      </c>
-      <c r="AS7">
-        <v>2.25</v>
-      </c>
-      <c r="AT7">
-        <v>2.65</v>
-      </c>
-      <c r="AU7">
-        <v>3.45</v>
-      </c>
-      <c r="AV7">
-        <v>2.54</v>
-      </c>
-      <c r="AW7">
-        <v>1.95</v>
-      </c>
-      <c r="AX7">
-        <v>1.6</v>
-      </c>
-      <c r="AY7">
-        <v>1.41</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.88</v>
-      </c>
-      <c r="BC7">
-        <v>2.05</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>150</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45806.5</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45806</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
         <v>75</v>
       </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>93</v>
-      </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L8">
         <v>1.85</v>
@@ -2127,93 +1800,39 @@
         <v>1.2</v>
       </c>
       <c r="AJ8" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK8" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL8">
-        <v>1.3</v>
-      </c>
-      <c r="AM8">
-        <v>1.26</v>
-      </c>
-      <c r="AN8">
-        <v>1.78</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>1.13</v>
-      </c>
-      <c r="AQ8">
-        <v>1.28</v>
-      </c>
-      <c r="AR8">
-        <v>1.52</v>
-      </c>
-      <c r="AS8">
-        <v>1.91</v>
-      </c>
-      <c r="AT8">
-        <v>2.42</v>
-      </c>
-      <c r="AU8">
-        <v>4.55</v>
-      </c>
-      <c r="AV8">
-        <v>3.08</v>
-      </c>
-      <c r="AW8">
-        <v>2.3</v>
-      </c>
-      <c r="AX8">
-        <v>1.8</v>
-      </c>
-      <c r="AY8">
-        <v>1.47</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.57</v>
-      </c>
-      <c r="BC8">
-        <v>2.4</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>154</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45806.54166666666</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45806</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
         <v>76</v>
       </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>94</v>
-      </c>
       <c r="F9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2222,356 +1841,248 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L9">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="M9">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="N9">
-        <v>2.49</v>
+        <v>5.8</v>
       </c>
       <c r="O9">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="P9">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>1.73</v>
+        <v>3.75</v>
       </c>
       <c r="R9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T9">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="U9">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AA9">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC9">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AD9">
         <v>3.2</v>
       </c>
       <c r="AE9">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH9">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI9">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="AK9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL9">
-        <v>1.57</v>
-      </c>
-      <c r="AM9">
-        <v>1.31</v>
-      </c>
-      <c r="AN9">
-        <v>1.38</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>1.24</v>
-      </c>
-      <c r="AQ9">
-        <v>1.42</v>
-      </c>
-      <c r="AR9">
-        <v>1.68</v>
-      </c>
-      <c r="AS9">
-        <v>2.05</v>
-      </c>
-      <c r="AT9">
-        <v>2.55</v>
-      </c>
-      <c r="AU9">
-        <v>3.55</v>
-      </c>
-      <c r="AV9">
-        <v>2.65</v>
-      </c>
-      <c r="AW9">
-        <v>2.05</v>
-      </c>
-      <c r="AX9">
-        <v>1.68</v>
-      </c>
-      <c r="AY9">
-        <v>1.43</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>2.1</v>
-      </c>
-      <c r="BC9">
-        <v>1.73</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>133</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45806.54166666666</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45806</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L10">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="M10">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="N10">
-        <v>5.8</v>
+        <v>2.49</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="P10">
+        <v>8.5</v>
+      </c>
+      <c r="Q10">
+        <v>1.73</v>
+      </c>
+      <c r="R10">
+        <v>1.33</v>
+      </c>
+      <c r="S10">
+        <v>3.25</v>
+      </c>
+      <c r="T10">
+        <v>2.63</v>
+      </c>
+      <c r="U10">
+        <v>1.44</v>
+      </c>
+      <c r="V10">
+        <v>7</v>
+      </c>
+      <c r="W10">
+        <v>1.1</v>
+      </c>
+      <c r="X10">
+        <v>1.05</v>
+      </c>
+      <c r="Y10">
         <v>10</v>
       </c>
-      <c r="Q10">
+      <c r="Z10">
+        <v>1.28</v>
+      </c>
+      <c r="AA10">
         <v>3.75</v>
       </c>
-      <c r="R10">
-        <v>1.36</v>
-      </c>
-      <c r="S10">
-        <v>2.78</v>
-      </c>
-      <c r="T10">
-        <v>2.74</v>
-      </c>
-      <c r="U10">
-        <v>1.38</v>
-      </c>
-      <c r="V10">
-        <v>6.8</v>
-      </c>
-      <c r="W10">
-        <v>1.07</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z10">
-        <v>1.29</v>
-      </c>
-      <c r="AA10">
-        <v>3.3</v>
-      </c>
       <c r="AB10">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AC10">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AD10">
         <v>3.2</v>
       </c>
       <c r="AE10">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF10">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ10" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK10" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL10">
-        <v>1.08</v>
-      </c>
-      <c r="AM10">
-        <v>1.22</v>
-      </c>
-      <c r="AN10">
-        <v>2.4</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.36</v>
-      </c>
-      <c r="BC10">
-        <v>3.75</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>137</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45806.54166666666</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45806</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L11">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="M11">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N11">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O11">
         <v>1.67</v>
@@ -2583,19 +2094,19 @@
         <v>2.55</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="T11">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V11">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W11">
         <v>1.1</v>
@@ -2610,308 +2121,200 @@
         <v>1.25</v>
       </c>
       <c r="AA11">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AB11">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC11">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AD11">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AE11">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AF11">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH11">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AI11">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL11">
-        <v>1.29</v>
-      </c>
-      <c r="AM11">
-        <v>1.25</v>
-      </c>
-      <c r="AN11">
-        <v>1.88</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>1.16</v>
-      </c>
-      <c r="AQ11">
-        <v>1.3</v>
-      </c>
-      <c r="AR11">
-        <v>1.54</v>
-      </c>
-      <c r="AS11">
-        <v>1.78</v>
-      </c>
-      <c r="AT11">
-        <v>2.21</v>
-      </c>
-      <c r="AU11">
-        <v>4.35</v>
-      </c>
-      <c r="AV11">
-        <v>3.07</v>
-      </c>
-      <c r="AW11">
-        <v>2.38</v>
-      </c>
-      <c r="AX11">
-        <v>1.88</v>
-      </c>
-      <c r="AY11">
-        <v>1.54</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.67</v>
-      </c>
-      <c r="BC11">
-        <v>2.55</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>130</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45806.54166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45806</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L12">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="M12">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N12">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="P12">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q12">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
         <v>1.2</v>
       </c>
       <c r="S12">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T12">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="U12">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V12">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="W12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z12">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AA12">
-        <v>6.36</v>
+        <v>5.8</v>
       </c>
       <c r="AB12">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AC12">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AD12">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE12">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AF12">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AG12">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH12">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="AI12">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AJ12" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL12">
-        <v>1.22</v>
-      </c>
-      <c r="AM12">
-        <v>1.22</v>
-      </c>
-      <c r="AN12">
-        <v>1.24</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>1.1</v>
-      </c>
-      <c r="AQ12">
-        <v>1.14</v>
-      </c>
-      <c r="AR12">
-        <v>1.4</v>
-      </c>
-      <c r="AS12">
-        <v>1.53</v>
-      </c>
-      <c r="AT12">
-        <v>1.85</v>
-      </c>
-      <c r="AU12">
-        <v>5.75</v>
-      </c>
-      <c r="AV12">
-        <v>4</v>
-      </c>
-      <c r="AW12">
-        <v>3.04</v>
-      </c>
-      <c r="AX12">
-        <v>2.25</v>
-      </c>
-      <c r="AY12">
-        <v>1.85</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>2.63</v>
-      </c>
-      <c r="BC12">
-        <v>1.44</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>155</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45806.55208333334</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45806</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L13">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="M13">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N13">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O13">
         <v>1.95</v>
@@ -2923,165 +2326,111 @@
         <v>1.88</v>
       </c>
       <c r="R13">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="T13">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="U13">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="V13">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="W13">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z13">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AA13">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB13">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AC13">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AE13">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AF13">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH13">
-        <v>3.78</v>
+        <v>4.4</v>
       </c>
       <c r="AI13">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ13" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="AK13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL13">
-        <v>1.4</v>
-      </c>
-      <c r="AM13">
-        <v>1.26</v>
-      </c>
-      <c r="AN13">
-        <v>1.65</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>1.09</v>
-      </c>
-      <c r="AQ13">
-        <v>1.2</v>
-      </c>
-      <c r="AR13">
-        <v>1.31</v>
-      </c>
-      <c r="AS13">
-        <v>1.6</v>
-      </c>
-      <c r="AT13">
-        <v>1.94</v>
-      </c>
-      <c r="AU13">
-        <v>5.6</v>
-      </c>
-      <c r="AV13">
-        <v>3.9</v>
-      </c>
-      <c r="AW13">
-        <v>2.92</v>
-      </c>
-      <c r="AX13">
-        <v>2.24</v>
-      </c>
-      <c r="AY13">
-        <v>1.8</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.95</v>
-      </c>
-      <c r="BC13">
-        <v>1.88</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45806.55208333334</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45806</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
         <v>129</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>148</v>
-      </c>
       <c r="L14">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
-        <v>5.3</v>
+        <v>5.24</v>
       </c>
       <c r="N14">
-        <v>6.8</v>
+        <v>6.58</v>
       </c>
       <c r="O14">
         <v>1.36</v>
@@ -3093,22 +2442,22 @@
         <v>3.2</v>
       </c>
       <c r="R14">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S14">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="T14">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="U14">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V14">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="W14">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -3117,293 +2466,185 @@
         <v>21</v>
       </c>
       <c r="Z14">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AA14">
         <v>6.5</v>
       </c>
       <c r="AB14">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD14">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AE14">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AF14">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH14">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AI14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ14" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL14">
-        <v>1.1</v>
-      </c>
-      <c r="AM14">
-        <v>1.14</v>
-      </c>
-      <c r="AN14">
-        <v>3</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>1.1</v>
-      </c>
-      <c r="AQ14">
-        <v>1.17</v>
-      </c>
-      <c r="AR14">
-        <v>1.42</v>
-      </c>
-      <c r="AS14">
-        <v>1.61</v>
-      </c>
-      <c r="AT14">
-        <v>1.95</v>
-      </c>
-      <c r="AU14">
-        <v>5.45</v>
-      </c>
-      <c r="AV14">
-        <v>4.05</v>
-      </c>
-      <c r="AW14">
-        <v>2.78</v>
-      </c>
-      <c r="AX14">
-        <v>2.25</v>
-      </c>
-      <c r="AY14">
-        <v>1.77</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.36</v>
-      </c>
-      <c r="BC14">
-        <v>3.2</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>157</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45806.55208333334</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45806</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L15">
-        <v>1.97</v>
+        <v>4.2</v>
       </c>
       <c r="M15">
-        <v>3.73</v>
+        <v>4.2</v>
       </c>
       <c r="N15">
-        <v>3.09</v>
+        <v>1.92</v>
       </c>
       <c r="O15">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="P15">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q15">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="R15">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="S15">
-        <v>3.6</v>
+        <v>4.65</v>
       </c>
       <c r="T15">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="U15">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="V15">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="Z15">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AB15">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AC15">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AD15">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AE15">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AF15">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AG15">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH15">
-        <v>3.7</v>
+        <v>2.71</v>
       </c>
       <c r="AI15">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AJ15" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK15" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL15">
-        <v>1.25</v>
-      </c>
-      <c r="AM15">
-        <v>1.25</v>
-      </c>
-      <c r="AN15">
-        <v>1.75</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>1.11</v>
-      </c>
-      <c r="AQ15">
-        <v>1.19</v>
-      </c>
-      <c r="AR15">
-        <v>1.27</v>
-      </c>
-      <c r="AS15">
-        <v>1.5</v>
-      </c>
-      <c r="AT15">
-        <v>1.92</v>
-      </c>
-      <c r="AU15">
-        <v>5.5</v>
-      </c>
-      <c r="AV15">
-        <v>3.98</v>
-      </c>
-      <c r="AW15">
-        <v>3.14</v>
-      </c>
-      <c r="AX15">
-        <v>2.25</v>
-      </c>
-      <c r="AY15">
-        <v>1.86</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.67</v>
-      </c>
-      <c r="BC15">
-        <v>2.2</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>158</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45806.55208333334</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45806</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3412,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L16">
         <v>2.2</v>
@@ -3463,10 +2704,10 @@
         <v>4.16</v>
       </c>
       <c r="AB16">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC16">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AD16">
         <v>2.64</v>
@@ -3487,430 +2728,268 @@
         <v>1.17</v>
       </c>
       <c r="AJ16" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL16">
-        <v>1.36</v>
-      </c>
-      <c r="AM16">
-        <v>1.22</v>
-      </c>
-      <c r="AN16">
-        <v>1.53</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>1.3</v>
-      </c>
-      <c r="AQ16">
-        <v>1.52</v>
-      </c>
-      <c r="AR16">
-        <v>1.85</v>
-      </c>
-      <c r="AS16">
-        <v>2.33</v>
-      </c>
-      <c r="AT16">
-        <v>3.05</v>
-      </c>
-      <c r="AU16">
-        <v>3.15</v>
-      </c>
-      <c r="AV16">
-        <v>2.33</v>
-      </c>
-      <c r="AW16">
-        <v>1.83</v>
-      </c>
-      <c r="AX16">
-        <v>1.52</v>
-      </c>
-      <c r="AY16">
-        <v>1.32</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.85</v>
-      </c>
-      <c r="BC16">
-        <v>2.1</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45806.5625</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45806</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F17" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L17">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="M17">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="N17">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="O17">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="P17">
-        <v>16.25</v>
+        <v>12</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S17">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="T17">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="U17">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="V17">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="Z17">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AA17">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AB17">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AC17">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AD17">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="AE17">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AH17">
-        <v>4.88</v>
+        <v>5.17</v>
       </c>
       <c r="AI17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ17" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL17">
-        <v>1.14</v>
-      </c>
-      <c r="AM17">
-        <v>1.18</v>
-      </c>
-      <c r="AN17">
-        <v>2.78</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>1.19</v>
-      </c>
-      <c r="AQ17">
-        <v>1.33</v>
-      </c>
-      <c r="AR17">
-        <v>1.53</v>
-      </c>
-      <c r="AS17">
-        <v>1.84</v>
-      </c>
-      <c r="AT17">
-        <v>2.36</v>
-      </c>
-      <c r="AU17">
-        <v>4.1</v>
-      </c>
-      <c r="AV17">
-        <v>3.05</v>
-      </c>
-      <c r="AW17">
-        <v>2.3</v>
-      </c>
-      <c r="AX17">
-        <v>1.83</v>
-      </c>
-      <c r="AY17">
-        <v>1.56</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.37</v>
-      </c>
-      <c r="BC17">
-        <v>3.2</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45806.58333333334</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45806</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
         <v>85</v>
       </c>
-      <c r="E18" t="s">
-        <v>103</v>
-      </c>
       <c r="F18" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L18">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="M18">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="N18">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="P18">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R18">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="S18">
-        <v>3.24</v>
+        <v>1.89</v>
       </c>
       <c r="T18">
-        <v>2.61</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="V18">
-        <v>6.3</v>
+        <v>14</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="Y18">
-        <v>10.4</v>
+        <v>4</v>
       </c>
       <c r="Z18">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="AA18">
-        <v>3.92</v>
+        <v>1.98</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>2.88</v>
       </c>
       <c r="AC18">
-        <v>2.03</v>
+        <v>1.26</v>
       </c>
       <c r="AD18">
-        <v>2.85</v>
+        <v>6.4</v>
       </c>
       <c r="AE18">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="AG18">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="AH18">
-        <v>5.17</v>
+        <v>14</v>
       </c>
       <c r="AI18">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AJ18" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL18">
-        <v>1.4</v>
-      </c>
-      <c r="AM18">
-        <v>1.31</v>
-      </c>
-      <c r="AN18">
-        <v>1.6</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>1.3</v>
-      </c>
-      <c r="AQ18">
-        <v>1.66</v>
-      </c>
-      <c r="AR18">
-        <v>2.09</v>
-      </c>
-      <c r="AS18">
-        <v>2.7</v>
-      </c>
-      <c r="AT18">
-        <v>3.4</v>
-      </c>
-      <c r="AU18">
-        <v>3.2</v>
-      </c>
-      <c r="AV18">
-        <v>2.16</v>
-      </c>
-      <c r="AW18">
-        <v>1.71</v>
-      </c>
-      <c r="AX18">
-        <v>1.41</v>
-      </c>
-      <c r="AY18">
-        <v>1.29</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.85</v>
-      </c>
-      <c r="BC18">
-        <v>2.1</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>161</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45806.58333333334</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45806</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
         <v>86</v>
       </c>
-      <c r="E19" t="s">
-        <v>104</v>
-      </c>
       <c r="F19" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -3922,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L19">
         <v>1.75</v>
@@ -3997,93 +3076,39 @@
         <v>1.06</v>
       </c>
       <c r="AJ19" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AK19" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL19">
-        <v>1.23</v>
-      </c>
-      <c r="AM19">
-        <v>1.21</v>
-      </c>
-      <c r="AN19">
-        <v>1.9</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.53</v>
-      </c>
-      <c r="BC19">
-        <v>3</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>131</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45806.58333333334</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45806</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4092,186 +3117,132 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L20">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="M20">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="N20">
-        <v>3.02</v>
+        <v>4.68</v>
       </c>
       <c r="O20">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="P20">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q20">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="R20">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S20">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T20">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U20">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="V20">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y20">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z20">
         <v>1.5</v>
       </c>
       <c r="AA20">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AB20">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AC20">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AD20">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AE20">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG20">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AH20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK20" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL20">
-        <v>1.36</v>
-      </c>
-      <c r="AM20">
-        <v>1.38</v>
-      </c>
-      <c r="AN20">
-        <v>1.52</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>1.65</v>
-      </c>
-      <c r="AQ20">
-        <v>2.07</v>
-      </c>
-      <c r="AR20">
-        <v>2.67</v>
-      </c>
-      <c r="AS20">
-        <v>3.6</v>
-      </c>
-      <c r="AT20">
-        <v>5</v>
-      </c>
-      <c r="AU20">
-        <v>2.1</v>
-      </c>
-      <c r="AV20">
-        <v>1.64</v>
-      </c>
-      <c r="AW20">
-        <v>1.34</v>
-      </c>
-      <c r="AX20">
-        <v>1.25</v>
-      </c>
-      <c r="AY20">
-        <v>1.12</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>2.05</v>
-      </c>
-      <c r="BC20">
-        <v>2.35</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>162</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45806.58333333334</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45806</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L21">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M21">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="N21">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
         <v>1.95</v>
@@ -4283,311 +3254,203 @@
         <v>3.2</v>
       </c>
       <c r="R21">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="S21">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="T21">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="U21">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="V21">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="W21">
+        <v>1.01</v>
+      </c>
+      <c r="X21">
+        <v>1.11</v>
+      </c>
+      <c r="Y21">
+        <v>5.3</v>
+      </c>
+      <c r="Z21">
+        <v>1.66</v>
+      </c>
+      <c r="AA21">
+        <v>2.23</v>
+      </c>
+      <c r="AB21">
+        <v>3.15</v>
+      </c>
+      <c r="AC21">
+        <v>1.34</v>
+      </c>
+      <c r="AD21">
+        <v>5.75</v>
+      </c>
+      <c r="AE21">
+        <v>1.12</v>
+      </c>
+      <c r="AF21">
+        <v>2.4</v>
+      </c>
+      <c r="AG21">
+        <v>1.46</v>
+      </c>
+      <c r="AH21">
+        <v>12.5</v>
+      </c>
+      <c r="AI21">
         <v>1.02</v>
       </c>
-      <c r="X21">
-        <v>1.22</v>
-      </c>
-      <c r="Y21">
-        <v>3.8</v>
-      </c>
-      <c r="Z21">
-        <v>1.78</v>
-      </c>
-      <c r="AA21">
-        <v>1.92</v>
-      </c>
-      <c r="AB21">
-        <v>3.64</v>
-      </c>
-      <c r="AC21">
-        <v>1.24</v>
-      </c>
-      <c r="AD21">
-        <v>7.5</v>
-      </c>
-      <c r="AE21">
-        <v>1.06</v>
-      </c>
-      <c r="AF21">
-        <v>2.62</v>
-      </c>
-      <c r="AG21">
-        <v>1.42</v>
-      </c>
-      <c r="AH21">
-        <v>20</v>
-      </c>
-      <c r="AI21">
-        <v>1.01</v>
-      </c>
       <c r="AJ21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AK21" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL21">
-        <v>1.5</v>
-      </c>
-      <c r="AM21">
-        <v>1.49</v>
-      </c>
-      <c r="AN21">
-        <v>1.52</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>1.56</v>
-      </c>
-      <c r="AQ21">
-        <v>2</v>
-      </c>
-      <c r="AR21">
-        <v>2.6</v>
-      </c>
-      <c r="AS21">
-        <v>3.35</v>
-      </c>
-      <c r="AT21">
-        <v>4.75</v>
-      </c>
-      <c r="AU21">
-        <v>2.2</v>
-      </c>
-      <c r="AV21">
-        <v>1.73</v>
-      </c>
-      <c r="AW21">
-        <v>1.44</v>
-      </c>
-      <c r="AX21">
-        <v>1.29</v>
-      </c>
-      <c r="AY21">
-        <v>1.15</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.95</v>
-      </c>
-      <c r="BC21">
-        <v>3.2</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>163</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45806.58333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45806</v>
       </c>
       <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
         <v>63</v>
       </c>
-      <c r="C22" t="s">
-        <v>81</v>
-      </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L22">
-        <v>3.78</v>
+        <v>1.44</v>
       </c>
       <c r="M22">
-        <v>2.41</v>
+        <v>4.75</v>
       </c>
       <c r="N22">
-        <v>2.27</v>
+        <v>6.02</v>
       </c>
       <c r="O22">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="P22">
+        <v>16.25</v>
+      </c>
+      <c r="Q22">
+        <v>3.2</v>
+      </c>
+      <c r="R22">
+        <v>1.27</v>
+      </c>
+      <c r="S22">
+        <v>3.2</v>
+      </c>
+      <c r="T22">
+        <v>2.54</v>
+      </c>
+      <c r="U22">
+        <v>1.53</v>
+      </c>
+      <c r="V22">
+        <v>4.7</v>
+      </c>
+      <c r="W22">
+        <v>1.12</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>15</v>
+      </c>
+      <c r="Z22">
+        <v>1.18</v>
+      </c>
+      <c r="AA22">
         <v>4.5</v>
       </c>
-      <c r="Q22">
-        <v>1.98</v>
-      </c>
-      <c r="R22">
-        <v>1.75</v>
-      </c>
-      <c r="S22">
-        <v>1.95</v>
-      </c>
-      <c r="T22">
-        <v>4.1</v>
-      </c>
-      <c r="U22">
+      <c r="AB22">
+        <v>1.63</v>
+      </c>
+      <c r="AC22">
+        <v>2.31</v>
+      </c>
+      <c r="AD22">
+        <v>2.53</v>
+      </c>
+      <c r="AE22">
+        <v>1.44</v>
+      </c>
+      <c r="AF22">
+        <v>1.78</v>
+      </c>
+      <c r="AG22">
+        <v>1.9</v>
+      </c>
+      <c r="AH22">
+        <v>4.93</v>
+      </c>
+      <c r="AI22">
         <v>1.18</v>
       </c>
-      <c r="V22">
-        <v>15</v>
-      </c>
-      <c r="W22">
-        <v>1.01</v>
-      </c>
-      <c r="X22">
-        <v>1.17</v>
-      </c>
-      <c r="Y22">
-        <v>4.33</v>
-      </c>
-      <c r="Z22">
-        <v>1.77</v>
-      </c>
-      <c r="AA22">
-        <v>1.93</v>
-      </c>
-      <c r="AB22">
-        <v>3.21</v>
-      </c>
-      <c r="AC22">
-        <v>1.3</v>
-      </c>
-      <c r="AD22">
-        <v>5.55</v>
-      </c>
-      <c r="AE22">
-        <v>1.09</v>
-      </c>
-      <c r="AF22">
-        <v>2.35</v>
-      </c>
-      <c r="AG22">
-        <v>1.53</v>
-      </c>
-      <c r="AH22">
-        <v>14</v>
-      </c>
-      <c r="AI22">
-        <v>1.01</v>
-      </c>
       <c r="AJ22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AK22" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL22">
-        <v>1.52</v>
-      </c>
-      <c r="AM22">
-        <v>1.44</v>
-      </c>
-      <c r="AN22">
-        <v>1.25</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>1.46</v>
-      </c>
-      <c r="AQ22">
-        <v>1.79</v>
-      </c>
-      <c r="AR22">
-        <v>2.77</v>
-      </c>
-      <c r="AS22">
-        <v>3.02</v>
-      </c>
-      <c r="AT22">
-        <v>4.15</v>
-      </c>
-      <c r="AU22">
-        <v>2.44</v>
-      </c>
-      <c r="AV22">
-        <v>1.9</v>
-      </c>
-      <c r="AW22">
-        <v>1.53</v>
-      </c>
-      <c r="AX22">
-        <v>1.33</v>
-      </c>
-      <c r="AY22">
-        <v>1.17</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>2.5</v>
-      </c>
-      <c r="BC22">
-        <v>1.98</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>164</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45806.58333333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45806</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4602,162 +3465,108 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L23">
-        <v>2.09</v>
+        <v>2.74</v>
       </c>
       <c r="M23">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="N23">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="P23">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q23">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="R23">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="S23">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="T23">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="U23">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
         <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="Z23">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AA23">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AB23">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="AC23">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AD23">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AE23">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AG23">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AH23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI23">
         <v>1.01</v>
       </c>
       <c r="AJ23" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK23" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL23">
-        <v>1.45</v>
-      </c>
-      <c r="AM23">
-        <v>1.42</v>
-      </c>
-      <c r="AN23">
-        <v>1.49</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>1.5</v>
-      </c>
-      <c r="AQ23">
-        <v>1.83</v>
-      </c>
-      <c r="AR23">
-        <v>2.39</v>
-      </c>
-      <c r="AS23">
-        <v>3.28</v>
-      </c>
-      <c r="AT23">
-        <v>4.25</v>
-      </c>
-      <c r="AU23">
-        <v>2.41</v>
-      </c>
-      <c r="AV23">
-        <v>1.83</v>
-      </c>
-      <c r="AW23">
-        <v>1.54</v>
-      </c>
-      <c r="AX23">
-        <v>1.25</v>
-      </c>
-      <c r="AY23">
-        <v>1.17</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.93</v>
-      </c>
-      <c r="BC23">
-        <v>2.65</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>131</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45806.58333333334</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45806</v>
       </c>
       <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
         <v>64</v>
       </c>
-      <c r="C24" t="s">
-        <v>82</v>
-      </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4772,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L24">
         <v>3.02</v>
@@ -4847,111 +3656,57 @@
         <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK24" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL24">
-        <v>1.39</v>
-      </c>
-      <c r="AM24">
-        <v>1.31</v>
-      </c>
-      <c r="AN24">
-        <v>1.55</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>1.28</v>
-      </c>
-      <c r="AQ24">
-        <v>1.49</v>
-      </c>
-      <c r="AR24">
-        <v>1.77</v>
-      </c>
-      <c r="AS24">
-        <v>2.2</v>
-      </c>
-      <c r="AT24">
-        <v>2.8</v>
-      </c>
-      <c r="AU24">
-        <v>3.3</v>
-      </c>
-      <c r="AV24">
-        <v>2.43</v>
-      </c>
-      <c r="AW24">
-        <v>1.92</v>
-      </c>
-      <c r="AX24">
-        <v>1.58</v>
-      </c>
-      <c r="AY24">
-        <v>1.37</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>1.88</v>
-      </c>
-      <c r="BC24">
-        <v>2.1</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>131</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45806.64583333334</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45806</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L25">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M25">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N25">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O25">
         <v>1.48</v>
@@ -4963,13 +3718,13 @@
         <v>2.95</v>
       </c>
       <c r="R25">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S25">
         <v>3.2</v>
       </c>
       <c r="T25">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
         <v>1.5</v>
@@ -4978,141 +3733,87 @@
         <v>5.5</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z25">
         <v>1.17</v>
       </c>
       <c r="AA25">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AB25">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC25">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD25">
         <v>2.59</v>
       </c>
       <c r="AE25">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH25">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AI25">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AJ25" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK25" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL25">
-        <v>1.25</v>
-      </c>
-      <c r="AM25">
-        <v>1.2</v>
-      </c>
-      <c r="AN25">
-        <v>2.3</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>1.11</v>
-      </c>
-      <c r="AQ25">
-        <v>1.22</v>
-      </c>
-      <c r="AR25">
-        <v>1.49</v>
-      </c>
-      <c r="AS25">
-        <v>1.67</v>
-      </c>
-      <c r="AT25">
-        <v>2.04</v>
-      </c>
-      <c r="AU25">
-        <v>5.2</v>
-      </c>
-      <c r="AV25">
-        <v>3.65</v>
-      </c>
-      <c r="AW25">
-        <v>2.68</v>
-      </c>
-      <c r="AX25">
-        <v>2.12</v>
-      </c>
-      <c r="AY25">
-        <v>1.72</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>1.48</v>
-      </c>
-      <c r="BC25">
-        <v>2.95</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>165</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45806.66666666666</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45806</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L26">
         <v>2.33</v>
@@ -5133,34 +3834,34 @@
         <v>1.83</v>
       </c>
       <c r="R26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S26">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T26">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="U26">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V26">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="W26">
         <v>1.28</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Z26">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AA26">
-        <v>7.25</v>
+        <v>8.5</v>
       </c>
       <c r="AB26">
         <v>1.27</v>
@@ -5175,102 +3876,48 @@
         <v>2.05</v>
       </c>
       <c r="AF26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG26">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AH26">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AI26">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AK26" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL26">
-        <v>1.5</v>
-      </c>
-      <c r="AM26">
-        <v>1.23</v>
-      </c>
-      <c r="AN26">
-        <v>1.54</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>1.15</v>
-      </c>
-      <c r="AR26">
-        <v>1.26</v>
-      </c>
-      <c r="AS26">
-        <v>1.42</v>
-      </c>
-      <c r="AT26">
-        <v>1.65</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>4.75</v>
-      </c>
-      <c r="AW26">
-        <v>3.6</v>
-      </c>
-      <c r="AX26">
-        <v>2.62</v>
-      </c>
-      <c r="AY26">
-        <v>2.1</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>1.83</v>
-      </c>
-      <c r="BC26">
-        <v>1.83</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>166</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45806.67708333334</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45806</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F27" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -5282,162 +3929,108 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
+        <v>129</v>
+      </c>
+      <c r="L27">
+        <v>1.14</v>
+      </c>
+      <c r="M27">
+        <v>6.9</v>
+      </c>
+      <c r="N27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O27">
+        <v>1.2</v>
+      </c>
+      <c r="P27">
+        <v>23</v>
+      </c>
+      <c r="Q27">
+        <v>4.33</v>
+      </c>
+      <c r="R27">
+        <v>1.17</v>
+      </c>
+      <c r="S27">
+        <v>5</v>
+      </c>
+      <c r="T27">
+        <v>1.8</v>
+      </c>
+      <c r="U27">
+        <v>1.91</v>
+      </c>
+      <c r="V27">
+        <v>3.5</v>
+      </c>
+      <c r="W27">
+        <v>1.29</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>29</v>
+      </c>
+      <c r="Z27">
+        <v>1.08</v>
+      </c>
+      <c r="AA27">
+        <v>7.5</v>
+      </c>
+      <c r="AB27">
+        <v>1.3</v>
+      </c>
+      <c r="AC27">
+        <v>3.33</v>
+      </c>
+      <c r="AD27">
+        <v>1.76</v>
+      </c>
+      <c r="AE27">
+        <v>1.94</v>
+      </c>
+      <c r="AF27">
+        <v>1.75</v>
+      </c>
+      <c r="AG27">
+        <v>2</v>
+      </c>
+      <c r="AH27">
+        <v>2.6</v>
+      </c>
+      <c r="AI27">
+        <v>1.48</v>
+      </c>
+      <c r="AJ27" t="s">
         <v>148</v>
       </c>
-      <c r="L27">
-        <v>1.97</v>
-      </c>
-      <c r="M27">
-        <v>2.9</v>
-      </c>
-      <c r="N27">
-        <v>3.74</v>
-      </c>
-      <c r="O27">
-        <v>1.67</v>
-      </c>
-      <c r="P27">
-        <v>6.25</v>
-      </c>
-      <c r="Q27">
-        <v>2.75</v>
-      </c>
-      <c r="R27">
-        <v>1.53</v>
-      </c>
-      <c r="S27">
-        <v>2.38</v>
-      </c>
-      <c r="T27">
-        <v>3.75</v>
-      </c>
-      <c r="U27">
-        <v>1.25</v>
-      </c>
-      <c r="V27">
-        <v>11</v>
-      </c>
-      <c r="W27">
-        <v>1.05</v>
-      </c>
-      <c r="X27">
-        <v>1.1</v>
-      </c>
-      <c r="Y27">
-        <v>6.5</v>
-      </c>
-      <c r="Z27">
-        <v>1.5</v>
-      </c>
-      <c r="AA27">
-        <v>2.5</v>
-      </c>
-      <c r="AB27">
-        <v>2.3</v>
-      </c>
-      <c r="AC27">
-        <v>1.5</v>
-      </c>
-      <c r="AD27">
-        <v>5</v>
-      </c>
-      <c r="AE27">
-        <v>1.17</v>
-      </c>
-      <c r="AF27">
-        <v>2.2</v>
-      </c>
-      <c r="AG27">
-        <v>1.62</v>
-      </c>
-      <c r="AH27">
-        <v>10</v>
-      </c>
-      <c r="AI27">
-        <v>1.04</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>149</v>
-      </c>
       <c r="AK27" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL27">
-        <v>1.25</v>
-      </c>
-      <c r="AM27">
-        <v>1.36</v>
-      </c>
-      <c r="AN27">
-        <v>1.7</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>1.43</v>
-      </c>
-      <c r="AQ27">
-        <v>1.72</v>
-      </c>
-      <c r="AR27">
-        <v>2.15</v>
-      </c>
-      <c r="AS27">
-        <v>2.75</v>
-      </c>
-      <c r="AT27">
-        <v>3.65</v>
-      </c>
-      <c r="AU27">
-        <v>2.55</v>
-      </c>
-      <c r="AV27">
-        <v>1.98</v>
-      </c>
-      <c r="AW27">
-        <v>1.61</v>
-      </c>
-      <c r="AX27">
-        <v>1.38</v>
-      </c>
-      <c r="AY27">
-        <v>1.22</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.67</v>
-      </c>
-      <c r="BC27">
-        <v>2.75</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>131</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45806.79166666666</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45806</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5452,165 +4045,111 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L28">
-        <v>1.14</v>
+        <v>1.97</v>
       </c>
       <c r="M28">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="N28">
-        <v>9.800000000000001</v>
+        <v>3.74</v>
       </c>
       <c r="O28">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="P28">
-        <v>23</v>
+        <v>6.25</v>
       </c>
       <c r="Q28">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="R28">
+        <v>1.53</v>
+      </c>
+      <c r="S28">
+        <v>2.38</v>
+      </c>
+      <c r="T28">
+        <v>3.75</v>
+      </c>
+      <c r="U28">
+        <v>1.25</v>
+      </c>
+      <c r="V28">
+        <v>11</v>
+      </c>
+      <c r="W28">
+        <v>1.05</v>
+      </c>
+      <c r="X28">
+        <v>1.1</v>
+      </c>
+      <c r="Y28">
+        <v>6.5</v>
+      </c>
+      <c r="Z28">
+        <v>1.5</v>
+      </c>
+      <c r="AA28">
+        <v>2.5</v>
+      </c>
+      <c r="AB28">
+        <v>2.3</v>
+      </c>
+      <c r="AC28">
+        <v>1.5</v>
+      </c>
+      <c r="AD28">
+        <v>5</v>
+      </c>
+      <c r="AE28">
         <v>1.17</v>
       </c>
-      <c r="S28">
-        <v>5</v>
-      </c>
-      <c r="T28">
-        <v>1.8</v>
-      </c>
-      <c r="U28">
-        <v>1.91</v>
-      </c>
-      <c r="V28">
-        <v>3.5</v>
-      </c>
-      <c r="W28">
-        <v>1.29</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>29</v>
-      </c>
-      <c r="Z28">
-        <v>1.08</v>
-      </c>
-      <c r="AA28">
-        <v>7.5</v>
-      </c>
-      <c r="AB28">
-        <v>1.3</v>
-      </c>
-      <c r="AC28">
-        <v>3.33</v>
-      </c>
-      <c r="AD28">
-        <v>1.76</v>
-      </c>
-      <c r="AE28">
-        <v>1.94</v>
-      </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH28">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="AI28">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="AJ28" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AK28" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL28">
-        <v>1.04</v>
-      </c>
-      <c r="AM28">
-        <v>1.09</v>
-      </c>
-      <c r="AN28">
-        <v>4.5</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>1.41</v>
-      </c>
-      <c r="AQ28">
-        <v>1.7</v>
-      </c>
-      <c r="AR28">
-        <v>2.1</v>
-      </c>
-      <c r="AS28">
-        <v>2.65</v>
-      </c>
-      <c r="AT28">
-        <v>3.45</v>
-      </c>
-      <c r="AU28">
-        <v>2.65</v>
-      </c>
-      <c r="AV28">
-        <v>2</v>
-      </c>
-      <c r="AW28">
-        <v>1.63</v>
-      </c>
-      <c r="AX28">
-        <v>1.41</v>
-      </c>
-      <c r="AY28">
-        <v>1.25</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.2</v>
-      </c>
-      <c r="BC28">
-        <v>4.33</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>131</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45806.79166666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45806</v>
       </c>
       <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" t="s">
         <v>68</v>
       </c>
-      <c r="C29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" t="s">
-        <v>86</v>
-      </c>
       <c r="E29" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -5622,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L29">
         <v>1.78</v>
@@ -5700,99 +4239,45 @@
         <v>149</v>
       </c>
       <c r="AK29" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL29">
-        <v>1.22</v>
-      </c>
-      <c r="AM29">
-        <v>1.3</v>
-      </c>
-      <c r="AN29">
-        <v>1.85</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>1.28</v>
-      </c>
-      <c r="AQ29">
-        <v>1.5</v>
-      </c>
-      <c r="AR29">
-        <v>1.81</v>
-      </c>
-      <c r="AS29">
-        <v>2.28</v>
-      </c>
-      <c r="AT29">
-        <v>2.9</v>
-      </c>
-      <c r="AU29">
-        <v>3.2</v>
-      </c>
-      <c r="AV29">
-        <v>2.4</v>
-      </c>
-      <c r="AW29">
-        <v>1.88</v>
-      </c>
-      <c r="AX29">
-        <v>1.55</v>
-      </c>
-      <c r="AY29">
-        <v>1.35</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.65</v>
-      </c>
-      <c r="BC29">
-        <v>2.6</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>131</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45806.89583333334</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45806</v>
       </c>
       <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" t="s">
         <v>68</v>
       </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>86</v>
-      </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L30">
         <v>2.49</v>
@@ -5867,111 +4352,57 @@
         <v>1.06</v>
       </c>
       <c r="AJ30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AK30" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL30">
-        <v>1.5</v>
-      </c>
-      <c r="AM30">
-        <v>1.3</v>
-      </c>
-      <c r="AN30">
-        <v>1.44</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>1.29</v>
-      </c>
-      <c r="AQ30">
-        <v>1.5</v>
-      </c>
-      <c r="AR30">
-        <v>1.82</v>
-      </c>
-      <c r="AS30">
-        <v>2.3</v>
-      </c>
-      <c r="AT30">
-        <v>2.9</v>
-      </c>
-      <c r="AU30">
-        <v>3.15</v>
-      </c>
-      <c r="AV30">
-        <v>2.38</v>
-      </c>
-      <c r="AW30">
-        <v>1.86</v>
-      </c>
-      <c r="AX30">
-        <v>1.54</v>
-      </c>
-      <c r="AY30">
-        <v>1.34</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>2.1</v>
-      </c>
-      <c r="BC30">
-        <v>1.83</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>131</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45806.89583333334</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45806</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L31">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="M31">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="N31">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="O31">
         <v>1.65</v>
@@ -5983,28 +4414,28 @@
         <v>2.75</v>
       </c>
       <c r="R31">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S31">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
         <v>1.26</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Z31">
         <v>1.5</v>
@@ -6013,90 +4444,36 @@
         <v>2.4</v>
       </c>
       <c r="AB31">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="AC31">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AD31">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
         <v>2.25</v>
       </c>
       <c r="AG31">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH31">
-        <v>9.1</v>
+        <v>11.5</v>
       </c>
       <c r="AI31">
         <v>1</v>
       </c>
       <c r="AJ31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AK31" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL31">
-        <v>1.33</v>
-      </c>
-      <c r="AM31">
-        <v>1.31</v>
-      </c>
-      <c r="AN31">
-        <v>1.85</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>1.27</v>
-      </c>
-      <c r="AQ31">
-        <v>1.48</v>
-      </c>
-      <c r="AR31">
-        <v>1.73</v>
-      </c>
-      <c r="AS31">
-        <v>2.1</v>
-      </c>
-      <c r="AT31">
-        <v>2.71</v>
-      </c>
-      <c r="AU31">
-        <v>3.6</v>
-      </c>
-      <c r="AV31">
-        <v>2.5</v>
-      </c>
-      <c r="AW31">
-        <v>2</v>
-      </c>
-      <c r="AX31">
-        <v>1.65</v>
-      </c>
-      <c r="AY31">
-        <v>1.38</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.65</v>
-      </c>
-      <c r="BC31">
-        <v>2.75</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>140</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45806.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-05-29.xlsx
+++ b/jogos_2025-05-29.xlsx
@@ -1149,35 +1149,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['5', '66', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['-1', '-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45806.5</v>
@@ -1278,26 +1278,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>6.82</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>14.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>1.54</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.33</v>
+        <v>7.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['5', '66', '90+1']</t>
+          <t>['19', '50', '60', '87']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45806.5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="N8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.54</v>
-      </c>
       <c r="P8" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.9</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['19', '50', '60', '87']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.25</v>
+        <v>2.63</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.4</v>
+        <v>1.57</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45806.5</v>
@@ -1536,35 +1536,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="M9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.8</v>
       </c>
-      <c r="N9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.36</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['34', '89']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['-1', '-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45806.54166666666</v>
@@ -1794,32 +1794,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>2.4</v>
       </c>
       <c r="P11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['34', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['11', '48', '72']</t>
         </is>
       </c>
       <c r="AG11" t="n">
         <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45806.54166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2.4</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['11', '48', '72']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45806.54166666666</v>
@@ -2826,26 +2826,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.89</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45806.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>1.89</v>
+        <v>3.24</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="U20" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.72</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>1.98</v>
+        <v>3.92</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.88</v>
+        <v>1.76</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.26</v>
+        <v>2.03</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.4</v>
+        <v>2.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.58</v>
+        <v>2.27</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['46', '91', '105']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45806.58333333334</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="M21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.43</v>
       </c>
-      <c r="N21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Y21" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45806.58333333334</v>
@@ -3342,35 +3342,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>2.43</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.4</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AD23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AH23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45806.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="M24" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.32</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['46', '91', '105']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AI24" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45806.58333333334</v>
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4023,65 +4023,65 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.14</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>9.800000000000001</v>
+        <v>3.74</v>
       </c>
       <c r="O28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.5</v>
       </c>
-      <c r="P28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>9</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="X28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.17</v>
       </c>
-      <c r="S28" t="n">
-        <v>5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['52', '53', '56', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45806.79166666666</v>
@@ -4126,16 +4126,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>1.14</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="N29" t="n">
-        <v>3.74</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="V29" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.5</v>
+        <v>3.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.17</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
+          <t>['52', '53', '56', '82']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45806.79166666666</v>
